--- a/news_daily/2026-08-17.xlsx
+++ b/news_daily/2026-08-17.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BH$55</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BH$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BH$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BH$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -43,7 +43,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -65,11 +65,6 @@
         <fgColor rgb="00FFE0B2"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFCDD2"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -89,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -101,9 +96,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -471,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH55"/>
+  <dimension ref="A1:BL55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -534,6 +526,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -835,6 +831,26 @@
       <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Ticker稽核警示</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
         </is>
       </c>
     </row>
@@ -1011,6 +1027,10 @@
       </c>
       <c r="BG2" s="2" t="inlineStr"/>
       <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr"/>
+      <c r="BL2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1177,6 +1197,10 @@
       <c r="BF3" s="2" t="inlineStr"/>
       <c r="BG3" s="2" t="inlineStr"/>
       <c r="BH3" s="2" t="inlineStr"/>
+      <c r="BI3" s="2" t="inlineStr"/>
+      <c r="BJ3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr"/>
+      <c r="BL3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1343,6 +1367,10 @@
       <c r="BF4" s="2" t="inlineStr"/>
       <c r="BG4" s="2" t="inlineStr"/>
       <c r="BH4" s="2" t="inlineStr"/>
+      <c r="BI4" s="2" t="inlineStr"/>
+      <c r="BJ4" s="2" t="inlineStr"/>
+      <c r="BK4" s="2" t="inlineStr"/>
+      <c r="BL4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -1517,6 +1545,10 @@
         </is>
       </c>
       <c r="BH5" s="3" t="inlineStr"/>
+      <c r="BI5" s="3" t="inlineStr"/>
+      <c r="BJ5" s="3" t="inlineStr"/>
+      <c r="BK5" s="3" t="inlineStr"/>
+      <c r="BL5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -1683,6 +1715,10 @@
         </is>
       </c>
       <c r="BH6" s="3" t="inlineStr"/>
+      <c r="BI6" s="3" t="inlineStr"/>
+      <c r="BJ6" s="3" t="inlineStr"/>
+      <c r="BK6" s="3" t="inlineStr"/>
+      <c r="BL6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -1857,6 +1893,10 @@
         </is>
       </c>
       <c r="BH7" s="3" t="inlineStr"/>
+      <c r="BI7" s="3" t="inlineStr"/>
+      <c r="BJ7" s="3" t="inlineStr"/>
+      <c r="BK7" s="3" t="inlineStr"/>
+      <c r="BL7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -2031,6 +2071,10 @@
         </is>
       </c>
       <c r="BH8" s="3" t="inlineStr"/>
+      <c r="BI8" s="3" t="inlineStr"/>
+      <c r="BJ8" s="3" t="inlineStr"/>
+      <c r="BK8" s="3" t="inlineStr"/>
+      <c r="BL8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2197,6 +2241,10 @@
         </is>
       </c>
       <c r="BH9" s="2" t="inlineStr"/>
+      <c r="BI9" s="2" t="inlineStr"/>
+      <c r="BJ9" s="2" t="inlineStr"/>
+      <c r="BK9" s="2" t="inlineStr"/>
+      <c r="BL9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -2363,6 +2411,10 @@
       <c r="BF10" s="3" t="inlineStr"/>
       <c r="BG10" s="3" t="inlineStr"/>
       <c r="BH10" s="3" t="inlineStr"/>
+      <c r="BI10" s="3" t="inlineStr"/>
+      <c r="BJ10" s="3" t="inlineStr"/>
+      <c r="BK10" s="3" t="inlineStr"/>
+      <c r="BL10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2537,6 +2589,10 @@
         </is>
       </c>
       <c r="BH11" s="2" t="inlineStr"/>
+      <c r="BI11" s="2" t="inlineStr"/>
+      <c r="BJ11" s="2" t="inlineStr"/>
+      <c r="BK11" s="2" t="inlineStr"/>
+      <c r="BL11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2711,6 +2767,10 @@
         </is>
       </c>
       <c r="BH12" s="2" t="inlineStr"/>
+      <c r="BI12" s="2" t="inlineStr"/>
+      <c r="BJ12" s="2" t="inlineStr"/>
+      <c r="BK12" s="2" t="inlineStr"/>
+      <c r="BL12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -2885,6 +2945,10 @@
       </c>
       <c r="BG13" s="2" t="inlineStr"/>
       <c r="BH13" s="2" t="inlineStr"/>
+      <c r="BI13" s="2" t="inlineStr"/>
+      <c r="BJ13" s="2" t="inlineStr"/>
+      <c r="BK13" s="2" t="inlineStr"/>
+      <c r="BL13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -2935,13 +2999,17 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L14" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N14" s="4" t="inlineStr">
@@ -2994,7 +3062,11 @@
         </is>
       </c>
       <c r="AA14" s="4" t="inlineStr"/>
-      <c r="AB14" s="4" t="inlineStr"/>
+      <c r="AB14" s="4" t="inlineStr">
+        <is>
+          <t>95e5975c26d94c3982698dda68748d10</t>
+        </is>
+      </c>
       <c r="AC14" s="4" t="inlineStr">
         <is>
           <t>b533b8bea98bf27fa55b6f81</t>
@@ -3015,7 +3087,11 @@
       <c r="AL14" s="4" t="inlineStr"/>
       <c r="AM14" s="4" t="inlineStr"/>
       <c r="AN14" s="4" t="inlineStr"/>
-      <c r="AO14" s="4" t="inlineStr"/>
+      <c r="AO14" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP14" s="4" t="inlineStr"/>
       <c r="AQ14" s="4" t="inlineStr"/>
       <c r="AR14" s="4" t="inlineStr"/>
@@ -3059,6 +3135,18 @@
         </is>
       </c>
       <c r="BH14" s="4" t="inlineStr"/>
+      <c r="BI14" s="4" t="inlineStr"/>
+      <c r="BJ14" s="4" t="inlineStr"/>
+      <c r="BK14" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL14" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -3233,6 +3321,10 @@
         </is>
       </c>
       <c r="BH15" s="3" t="inlineStr"/>
+      <c r="BI15" s="3" t="inlineStr"/>
+      <c r="BJ15" s="3" t="inlineStr"/>
+      <c r="BK15" s="3" t="inlineStr"/>
+      <c r="BL15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3399,6 +3491,10 @@
       <c r="BF16" s="2" t="inlineStr"/>
       <c r="BG16" s="2" t="inlineStr"/>
       <c r="BH16" s="2" t="inlineStr"/>
+      <c r="BI16" s="2" t="inlineStr"/>
+      <c r="BJ16" s="2" t="inlineStr"/>
+      <c r="BK16" s="2" t="inlineStr"/>
+      <c r="BL16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3565,6 +3661,10 @@
       <c r="BF17" s="2" t="inlineStr"/>
       <c r="BG17" s="2" t="inlineStr"/>
       <c r="BH17" s="2" t="inlineStr"/>
+      <c r="BI17" s="2" t="inlineStr"/>
+      <c r="BJ17" s="2" t="inlineStr"/>
+      <c r="BK17" s="2" t="inlineStr"/>
+      <c r="BL17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3739,6 +3839,10 @@
         </is>
       </c>
       <c r="BH18" s="2" t="inlineStr"/>
+      <c r="BI18" s="2" t="inlineStr"/>
+      <c r="BJ18" s="2" t="inlineStr"/>
+      <c r="BK18" s="2" t="inlineStr"/>
+      <c r="BL18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -3905,6 +4009,10 @@
       <c r="BF19" s="2" t="inlineStr"/>
       <c r="BG19" s="2" t="inlineStr"/>
       <c r="BH19" s="2" t="inlineStr"/>
+      <c r="BI19" s="2" t="inlineStr"/>
+      <c r="BJ19" s="2" t="inlineStr"/>
+      <c r="BK19" s="2" t="inlineStr"/>
+      <c r="BL19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -4079,6 +4187,10 @@
       </c>
       <c r="BG20" s="3" t="inlineStr"/>
       <c r="BH20" s="3" t="inlineStr"/>
+      <c r="BI20" s="3" t="inlineStr"/>
+      <c r="BJ20" s="3" t="inlineStr"/>
+      <c r="BK20" s="3" t="inlineStr"/>
+      <c r="BL20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4253,6 +4365,10 @@
       </c>
       <c r="BG21" s="2" t="inlineStr"/>
       <c r="BH21" s="2" t="inlineStr"/>
+      <c r="BI21" s="2" t="inlineStr"/>
+      <c r="BJ21" s="2" t="inlineStr"/>
+      <c r="BK21" s="2" t="inlineStr"/>
+      <c r="BL21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4419,6 +4535,10 @@
       <c r="BF22" s="2" t="inlineStr"/>
       <c r="BG22" s="2" t="inlineStr"/>
       <c r="BH22" s="2" t="inlineStr"/>
+      <c r="BI22" s="2" t="inlineStr"/>
+      <c r="BJ22" s="2" t="inlineStr"/>
+      <c r="BK22" s="2" t="inlineStr"/>
+      <c r="BL22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4593,6 +4713,10 @@
       </c>
       <c r="BG23" s="2" t="inlineStr"/>
       <c r="BH23" s="2" t="inlineStr"/>
+      <c r="BI23" s="2" t="inlineStr"/>
+      <c r="BJ23" s="2" t="inlineStr"/>
+      <c r="BK23" s="2" t="inlineStr"/>
+      <c r="BL23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4767,6 +4891,10 @@
         </is>
       </c>
       <c r="BH24" s="2" t="inlineStr"/>
+      <c r="BI24" s="2" t="inlineStr"/>
+      <c r="BJ24" s="2" t="inlineStr"/>
+      <c r="BK24" s="2" t="inlineStr"/>
+      <c r="BL24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -4941,6 +5069,10 @@
         </is>
       </c>
       <c r="BH25" s="3" t="inlineStr"/>
+      <c r="BI25" s="3" t="inlineStr"/>
+      <c r="BJ25" s="3" t="inlineStr"/>
+      <c r="BK25" s="3" t="inlineStr"/>
+      <c r="BL25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -5115,6 +5247,10 @@
         </is>
       </c>
       <c r="BH26" s="3" t="inlineStr"/>
+      <c r="BI26" s="3" t="inlineStr"/>
+      <c r="BJ26" s="3" t="inlineStr"/>
+      <c r="BK26" s="3" t="inlineStr"/>
+      <c r="BL26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -5281,6 +5417,10 @@
         </is>
       </c>
       <c r="BH27" s="3" t="inlineStr"/>
+      <c r="BI27" s="3" t="inlineStr"/>
+      <c r="BJ27" s="3" t="inlineStr"/>
+      <c r="BK27" s="3" t="inlineStr"/>
+      <c r="BL27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -5447,6 +5587,10 @@
       <c r="BF28" s="3" t="inlineStr"/>
       <c r="BG28" s="3" t="inlineStr"/>
       <c r="BH28" s="3" t="inlineStr"/>
+      <c r="BI28" s="3" t="inlineStr"/>
+      <c r="BJ28" s="3" t="inlineStr"/>
+      <c r="BK28" s="3" t="inlineStr"/>
+      <c r="BL28" s="3" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -5621,6 +5765,10 @@
         </is>
       </c>
       <c r="BH29" s="3" t="inlineStr"/>
+      <c r="BI29" s="3" t="inlineStr"/>
+      <c r="BJ29" s="3" t="inlineStr"/>
+      <c r="BK29" s="3" t="inlineStr"/>
+      <c r="BL29" s="3" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
@@ -5795,6 +5943,10 @@
         </is>
       </c>
       <c r="BH30" s="3" t="inlineStr"/>
+      <c r="BI30" s="3" t="inlineStr"/>
+      <c r="BJ30" s="3" t="inlineStr"/>
+      <c r="BK30" s="3" t="inlineStr"/>
+      <c r="BL30" s="3" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -5969,6 +6121,10 @@
         </is>
       </c>
       <c r="BH31" s="2" t="inlineStr"/>
+      <c r="BI31" s="2" t="inlineStr"/>
+      <c r="BJ31" s="2" t="inlineStr"/>
+      <c r="BK31" s="2" t="inlineStr"/>
+      <c r="BL31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -6143,6 +6299,10 @@
         </is>
       </c>
       <c r="BH32" s="3" t="inlineStr"/>
+      <c r="BI32" s="3" t="inlineStr"/>
+      <c r="BJ32" s="3" t="inlineStr"/>
+      <c r="BK32" s="3" t="inlineStr"/>
+      <c r="BL32" s="3" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -6317,6 +6477,10 @@
       </c>
       <c r="BG33" s="3" t="inlineStr"/>
       <c r="BH33" s="3" t="inlineStr"/>
+      <c r="BI33" s="3" t="inlineStr"/>
+      <c r="BJ33" s="3" t="inlineStr"/>
+      <c r="BK33" s="3" t="inlineStr"/>
+      <c r="BL33" s="3" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6491,6 +6655,10 @@
         </is>
       </c>
       <c r="BH34" s="2" t="inlineStr"/>
+      <c r="BI34" s="2" t="inlineStr"/>
+      <c r="BJ34" s="2" t="inlineStr"/>
+      <c r="BK34" s="2" t="inlineStr"/>
+      <c r="BL34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6665,6 +6833,10 @@
         </is>
       </c>
       <c r="BH35" s="2" t="inlineStr"/>
+      <c r="BI35" s="2" t="inlineStr"/>
+      <c r="BJ35" s="2" t="inlineStr"/>
+      <c r="BK35" s="2" t="inlineStr"/>
+      <c r="BL35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -6715,13 +6887,17 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L36" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L36" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M36" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N36" s="4" t="inlineStr">
@@ -6774,7 +6950,11 @@
         </is>
       </c>
       <c r="AA36" s="4" t="inlineStr"/>
-      <c r="AB36" s="4" t="inlineStr"/>
+      <c r="AB36" s="4" t="inlineStr">
+        <is>
+          <t>d023b0eb009747c18a67f1444cb80104</t>
+        </is>
+      </c>
       <c r="AC36" s="4" t="inlineStr">
         <is>
           <t>9fc0c06395e11a1f12ce636d</t>
@@ -6795,7 +6975,11 @@
       <c r="AL36" s="4" t="inlineStr"/>
       <c r="AM36" s="4" t="inlineStr"/>
       <c r="AN36" s="4" t="inlineStr"/>
-      <c r="AO36" s="4" t="inlineStr"/>
+      <c r="AO36" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP36" s="4" t="inlineStr"/>
       <c r="AQ36" s="4" t="inlineStr"/>
       <c r="AR36" s="4" t="inlineStr"/>
@@ -6839,6 +7023,18 @@
         </is>
       </c>
       <c r="BH36" s="4" t="inlineStr"/>
+      <c r="BI36" s="4" t="inlineStr"/>
+      <c r="BJ36" s="4" t="inlineStr"/>
+      <c r="BK36" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL36" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -6889,13 +7085,17 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L37" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L37" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N37" s="4" t="inlineStr">
@@ -6948,7 +7148,11 @@
         </is>
       </c>
       <c r="AA37" s="4" t="inlineStr"/>
-      <c r="AB37" s="4" t="inlineStr"/>
+      <c r="AB37" s="4" t="inlineStr">
+        <is>
+          <t>033742cfa14a4dc7a0f036c3839ff9c8</t>
+        </is>
+      </c>
       <c r="AC37" s="4" t="inlineStr">
         <is>
           <t>eab8ed09444f99fbe8f3f632</t>
@@ -6969,7 +7173,11 @@
       <c r="AL37" s="4" t="inlineStr"/>
       <c r="AM37" s="4" t="inlineStr"/>
       <c r="AN37" s="4" t="inlineStr"/>
-      <c r="AO37" s="4" t="inlineStr"/>
+      <c r="AO37" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP37" s="4" t="inlineStr"/>
       <c r="AQ37" s="4" t="inlineStr"/>
       <c r="AR37" s="4" t="inlineStr"/>
@@ -7005,520 +7213,608 @@
         </is>
       </c>
       <c r="BH37" s="4" t="inlineStr"/>
+      <c r="BI37" s="4" t="inlineStr"/>
+      <c r="BJ37" s="4" t="inlineStr"/>
+      <c r="BK37" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL37" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>WMT</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Walmart Inc.</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>2026-08-17T05:12:05+08:00</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Popular ice cream brand sold at Walmart and Target files for bankruptcy</t>
         </is>
       </c>
-      <c r="G38" s="5" t="inlineStr"/>
-      <c r="H38" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I38" s="5" t="inlineStr">
-        <is>
-          <t>破產</t>
-        </is>
-      </c>
-      <c r="J38" s="5" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K38" s="5" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L38" s="5" t="inlineStr"/>
-      <c r="M38" s="5" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>'-0.757</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr"/>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQZ2NOcHBBeFgwamJCQ0hNWmJkLXJHOTZjUU5aT1hVOEpfSzY1aW8wZ2NLMFVYNE5QZG5zLUxMTGYzWUQzLTV1SDJXbkRuZnJoWW92R250WmpMaXZEZFFHajBqU2Q2NG44aU1qX2hUOVdyZnhsQlYxeTVrakhOYTZyT3kzaWpNUGRWLWZ4andORUJrMm9nVzk0bQ?oc=5</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>沃爾瑪和塔吉特銷售的熱門冰淇淋品牌申請破產</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>FINANCIAL</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>bankruptcy</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr"/>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>908884f16e494d5c8614d055b7bf7e8a</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>35a1e5ff35be561beca55240</t>
+        </is>
+      </c>
+      <c r="AD38" s="2" t="inlineStr">
+        <is>
+          <t>101a5c0eec5ff35f912347c8</t>
+        </is>
+      </c>
+      <c r="AE38" s="2" t="inlineStr"/>
+      <c r="AF38" s="2" t="inlineStr"/>
+      <c r="AG38" s="2" t="inlineStr"/>
+      <c r="AH38" s="2" t="inlineStr"/>
+      <c r="AI38" s="2" t="inlineStr"/>
+      <c r="AJ38" s="2" t="inlineStr"/>
+      <c r="AK38" s="2" t="inlineStr"/>
+      <c r="AL38" s="2" t="inlineStr"/>
+      <c r="AM38" s="2" t="inlineStr"/>
+      <c r="AN38" s="2" t="inlineStr"/>
+      <c r="AO38" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N38" s="5" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O38" s="5" t="inlineStr">
-        <is>
-          <t>'-0.757</t>
-        </is>
-      </c>
-      <c r="P38" s="5" t="inlineStr"/>
-      <c r="Q38" s="5" t="inlineStr"/>
-      <c r="R38" s="5" t="inlineStr"/>
-      <c r="S38" s="5" t="inlineStr"/>
-      <c r="T38" s="5" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U38" s="5" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQZ2NOcHBBeFgwamJCQ0hNWmJkLXJHOTZjUU5aT1hVOEpfSzY1aW8wZ2NLMFVYNE5QZG5zLUxMTGYzWUQzLTV1SDJXbkRuZnJoWW92R250WmpMaXZEZFFHajBqU2Q2NG44aU1qX2hUOVdyZnhsQlYxeTVrakhOYTZyT3kzaWpNUGRWLWZ4andORUJrMm9nVzk0bQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V38" s="5" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W38" s="5" t="inlineStr">
-        <is>
-          <t>沃爾瑪和塔吉特銷售的熱門冰淇淋品牌申請破產</t>
-        </is>
-      </c>
-      <c r="X38" s="5" t="inlineStr">
-        <is>
-          <t>FINANCIAL</t>
-        </is>
-      </c>
-      <c r="Y38" s="5" t="inlineStr">
-        <is>
-          <t>BANKRUPTCY</t>
-        </is>
-      </c>
-      <c r="Z38" s="5" t="inlineStr">
-        <is>
-          <t>bankruptcy</t>
-        </is>
-      </c>
-      <c r="AA38" s="5" t="inlineStr"/>
-      <c r="AB38" s="5" t="inlineStr"/>
-      <c r="AC38" s="5" t="inlineStr">
-        <is>
-          <t>35a1e5ff35be561beca55240</t>
-        </is>
-      </c>
-      <c r="AD38" s="5" t="inlineStr">
-        <is>
-          <t>101a5c0eec5ff35f912347c8</t>
-        </is>
-      </c>
-      <c r="AE38" s="5" t="inlineStr"/>
-      <c r="AF38" s="5" t="inlineStr"/>
-      <c r="AG38" s="5" t="inlineStr"/>
-      <c r="AH38" s="5" t="inlineStr"/>
-      <c r="AI38" s="5" t="inlineStr"/>
-      <c r="AJ38" s="5" t="inlineStr"/>
-      <c r="AK38" s="5" t="inlineStr"/>
-      <c r="AL38" s="5" t="inlineStr"/>
-      <c r="AM38" s="5" t="inlineStr"/>
-      <c r="AN38" s="5" t="inlineStr"/>
-      <c r="AO38" s="5" t="inlineStr"/>
-      <c r="AP38" s="5" t="inlineStr"/>
-      <c r="AQ38" s="5" t="inlineStr"/>
-      <c r="AR38" s="5" t="inlineStr"/>
-      <c r="AS38" s="5" t="inlineStr"/>
-      <c r="AT38" s="5" t="inlineStr"/>
-      <c r="AU38" s="5" t="inlineStr"/>
-      <c r="AV38" s="5" t="inlineStr"/>
-      <c r="AW38" s="5" t="inlineStr">
+      <c r="AP38" s="2" t="inlineStr"/>
+      <c r="AQ38" s="2" t="inlineStr"/>
+      <c r="AR38" s="2" t="inlineStr"/>
+      <c r="AS38" s="2" t="inlineStr"/>
+      <c r="AT38" s="2" t="inlineStr"/>
+      <c r="AU38" s="2" t="inlineStr"/>
+      <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" s="2" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX38" s="5" t="inlineStr"/>
-      <c r="AY38" s="5" t="inlineStr"/>
-      <c r="AZ38" s="5" t="inlineStr"/>
-      <c r="BA38" s="5" t="inlineStr"/>
-      <c r="BB38" s="5" t="inlineStr">
+      <c r="AX38" s="2" t="inlineStr"/>
+      <c r="AY38" s="2" t="inlineStr"/>
+      <c r="AZ38" s="2" t="inlineStr"/>
+      <c r="BA38" s="2" t="inlineStr"/>
+      <c r="BB38" s="2" t="inlineStr">
         <is>
           <t>WMT</t>
         </is>
       </c>
-      <c r="BC38" s="5" t="inlineStr">
+      <c r="BC38" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD38" s="5" t="inlineStr"/>
-      <c r="BE38" s="5" t="inlineStr">
+      <c r="BD38" s="2" t="inlineStr"/>
+      <c r="BE38" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF38" s="5" t="inlineStr">
+      <c r="BF38" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG38" s="5" t="inlineStr">
+      <c r="BG38" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH38" s="5" t="inlineStr"/>
+      <c r="BH38" s="2" t="inlineStr"/>
+      <c r="BI38" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ38" s="2" t="inlineStr"/>
+      <c r="BK38" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL38" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="inlineStr">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr"/>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr"/>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Intercontinental Exchange</t>
         </is>
       </c>
-      <c r="E39" s="5" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>2026-08-17T05:12:05+08:00</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Popular ice cream brand sold at Walmart and Target files for bankruptcy</t>
         </is>
       </c>
-      <c r="G39" s="5" t="inlineStr"/>
-      <c r="H39" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I39" s="5" t="inlineStr">
-        <is>
-          <t>破產</t>
-        </is>
-      </c>
-      <c r="J39" s="5" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K39" s="5" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L39" s="5" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M39" s="5" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>'-0.757</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr"/>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t>主體證據不足</t>
+        </is>
+      </c>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQZ2NOcHBBeFgwamJCQ0hNWmJkLXJHOTZjUU5aT1hVOEpfSzY1aW8wZ2NLMFVYNE5QZG5zLUxMTGYzWUQzLTV1SDJXbkRuZnJoWW92R250WmpMaXZEZFFHajBqU2Q2NG44aU1qX2hUOVdyZnhsQlYxeTVrakhOYTZyT3kzaWpNUGRWLWZ4andORUJrMm9nVzk0bQ?oc=5</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>沃爾瑪和塔吉特銷售的熱門冰淇淋品牌申請破產</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>FINANCIAL</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>bankruptcy</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr"/>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>09f5ee74b0ae49ce8fb5d4cf7511c4a5</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>35a1e5ff35be561beca55240</t>
+        </is>
+      </c>
+      <c r="AD39" s="2" t="inlineStr">
+        <is>
+          <t>11dfdd497cf6d878e41e446f</t>
+        </is>
+      </c>
+      <c r="AE39" s="2" t="inlineStr"/>
+      <c r="AF39" s="2" t="inlineStr"/>
+      <c r="AG39" s="2" t="inlineStr"/>
+      <c r="AH39" s="2" t="inlineStr"/>
+      <c r="AI39" s="2" t="inlineStr"/>
+      <c r="AJ39" s="2" t="inlineStr"/>
+      <c r="AK39" s="2" t="inlineStr"/>
+      <c r="AL39" s="2" t="inlineStr"/>
+      <c r="AM39" s="2" t="inlineStr"/>
+      <c r="AN39" s="2" t="inlineStr"/>
+      <c r="AO39" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N39" s="5" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O39" s="5" t="inlineStr">
-        <is>
-          <t>'-0.757</t>
-        </is>
-      </c>
-      <c r="P39" s="5" t="inlineStr"/>
-      <c r="Q39" s="5" t="inlineStr"/>
-      <c r="R39" s="5" t="inlineStr"/>
-      <c r="S39" s="5" t="inlineStr"/>
-      <c r="T39" s="5" t="inlineStr">
+      <c r="AP39" s="2" t="inlineStr"/>
+      <c r="AQ39" s="2" t="inlineStr"/>
+      <c r="AR39" s="2" t="inlineStr"/>
+      <c r="AS39" s="2" t="inlineStr"/>
+      <c r="AT39" s="2" t="inlineStr"/>
+      <c r="AU39" s="2" t="inlineStr"/>
+      <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" s="2" t="inlineStr"/>
+      <c r="AX39" s="2" t="inlineStr"/>
+      <c r="AY39" s="2" t="inlineStr"/>
+      <c r="AZ39" s="2" t="inlineStr"/>
+      <c r="BA39" s="2" t="inlineStr"/>
+      <c r="BB39" s="2" t="inlineStr">
+        <is>
+          <t>ICE</t>
+        </is>
+      </c>
+      <c r="BC39" s="2" t="inlineStr">
         <is>
           <t>主體證據不足</t>
         </is>
       </c>
-      <c r="U39" s="5" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQZ2NOcHBBeFgwamJCQ0hNWmJkLXJHOTZjUU5aT1hVOEpfSzY1aW8wZ2NLMFVYNE5QZG5zLUxMTGYzWUQzLTV1SDJXbkRuZnJoWW92R250WmpMaXZEZFFHajBqU2Q2NG44aU1qX2hUOVdyZnhsQlYxeTVrakhOYTZyT3kzaWpNUGRWLWZ4andORUJrMm9nVzk0bQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V39" s="5" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W39" s="5" t="inlineStr">
-        <is>
-          <t>沃爾瑪和塔吉特銷售的熱門冰淇淋品牌申請破產</t>
-        </is>
-      </c>
-      <c r="X39" s="5" t="inlineStr">
-        <is>
-          <t>FINANCIAL</t>
-        </is>
-      </c>
-      <c r="Y39" s="5" t="inlineStr">
-        <is>
-          <t>BANKRUPTCY</t>
-        </is>
-      </c>
-      <c r="Z39" s="5" t="inlineStr">
-        <is>
-          <t>bankruptcy</t>
-        </is>
-      </c>
-      <c r="AA39" s="5" t="inlineStr"/>
-      <c r="AB39" s="5" t="inlineStr"/>
-      <c r="AC39" s="5" t="inlineStr">
-        <is>
-          <t>35a1e5ff35be561beca55240</t>
-        </is>
-      </c>
-      <c r="AD39" s="5" t="inlineStr">
-        <is>
-          <t>11dfdd497cf6d878e41e446f</t>
-        </is>
-      </c>
-      <c r="AE39" s="5" t="inlineStr"/>
-      <c r="AF39" s="5" t="inlineStr"/>
-      <c r="AG39" s="5" t="inlineStr"/>
-      <c r="AH39" s="5" t="inlineStr"/>
-      <c r="AI39" s="5" t="inlineStr"/>
-      <c r="AJ39" s="5" t="inlineStr"/>
-      <c r="AK39" s="5" t="inlineStr"/>
-      <c r="AL39" s="5" t="inlineStr"/>
-      <c r="AM39" s="5" t="inlineStr"/>
-      <c r="AN39" s="5" t="inlineStr"/>
-      <c r="AO39" s="5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP39" s="5" t="inlineStr"/>
-      <c r="AQ39" s="5" t="inlineStr"/>
-      <c r="AR39" s="5" t="inlineStr"/>
-      <c r="AS39" s="5" t="inlineStr"/>
-      <c r="AT39" s="5" t="inlineStr"/>
-      <c r="AU39" s="5" t="inlineStr"/>
-      <c r="AV39" s="5" t="inlineStr"/>
-      <c r="AW39" s="5" t="inlineStr"/>
-      <c r="AX39" s="5" t="inlineStr"/>
-      <c r="AY39" s="5" t="inlineStr"/>
-      <c r="AZ39" s="5" t="inlineStr"/>
-      <c r="BA39" s="5" t="inlineStr"/>
-      <c r="BB39" s="5" t="inlineStr">
+      <c r="BD39" s="2" t="inlineStr">
         <is>
           <t>ICE</t>
         </is>
       </c>
-      <c r="BC39" s="5" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD39" s="5" t="inlineStr">
-        <is>
-          <t>ICE</t>
-        </is>
-      </c>
-      <c r="BE39" s="5" t="inlineStr">
+      <c r="BE39" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF39" s="5" t="inlineStr">
+      <c r="BF39" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG39" s="5" t="inlineStr"/>
-      <c r="BH39" s="5" t="inlineStr"/>
+      <c r="BG39" s="2" t="inlineStr"/>
+      <c r="BH39" s="2" t="inlineStr"/>
+      <c r="BI39" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ39" s="2" t="inlineStr"/>
+      <c r="BK39" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL39" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:43:17.016263+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>COF</t>
         </is>
       </c>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Capital One</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>2026-08-17T05:06:39+08:00</t>
         </is>
       </c>
-      <c r="F40" s="4" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Boy George - Radio Interview (3 Jul 26) Capital One Class Action Lawsuit (61jGcnyHu9)</t>
         </is>
       </c>
-      <c r="G40" s="4" t="inlineStr"/>
-      <c r="H40" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I40" s="4" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K40" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L40" s="4" t="inlineStr"/>
-      <c r="M40" s="4" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>'-0.232</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr"/>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTFBsZlRfNXdiVjV3OTFrMGNxM2JOcmVOY2tWQloxeXJuZWJhenJmblc0VC1sOTRkZWxIeEhfNjR0T2tvTmJYLVJDd29HbWczMVkzNWZkUTNjQ2dBTHM?oc=5</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>Mshale</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>Boy George - 電台訪談（26 年 7 月 3 日）第一資本集體訴訟 (61jGcnyHu9)</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>class action</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr"/>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>87b4a47698524386a67eb3aa0b1cd7e7</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>3d5db05467b8c673cc133597</t>
+        </is>
+      </c>
+      <c r="AD40" s="2" t="inlineStr">
+        <is>
+          <t>23143c5a5dd4c31fa03783dd</t>
+        </is>
+      </c>
+      <c r="AE40" s="2" t="inlineStr"/>
+      <c r="AF40" s="2" t="inlineStr"/>
+      <c r="AG40" s="2" t="inlineStr"/>
+      <c r="AH40" s="2" t="inlineStr"/>
+      <c r="AI40" s="2" t="inlineStr"/>
+      <c r="AJ40" s="2" t="inlineStr"/>
+      <c r="AK40" s="2" t="inlineStr"/>
+      <c r="AL40" s="2" t="inlineStr"/>
+      <c r="AM40" s="2" t="inlineStr"/>
+      <c r="AN40" s="2" t="inlineStr"/>
+      <c r="AO40" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N40" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O40" s="4" t="inlineStr">
-        <is>
-          <t>'-0.232</t>
-        </is>
-      </c>
-      <c r="P40" s="4" t="inlineStr"/>
-      <c r="Q40" s="4" t="inlineStr"/>
-      <c r="R40" s="4" t="inlineStr"/>
-      <c r="S40" s="4" t="inlineStr"/>
-      <c r="T40" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U40" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTFBsZlRfNXdiVjV3OTFrMGNxM2JOcmVOY2tWQloxeXJuZWJhenJmblc0VC1sOTRkZWxIeEhfNjR0T2tvTmJYLVJDd29HbWczMVkzNWZkUTNjQ2dBTHM?oc=5</t>
-        </is>
-      </c>
-      <c r="V40" s="4" t="inlineStr">
-        <is>
-          <t>Mshale</t>
-        </is>
-      </c>
-      <c r="W40" s="4" t="inlineStr">
-        <is>
-          <t>Boy George - 電台訪談（26 年 7 月 3 日）第一資本集體訴訟 (61jGcnyHu9)</t>
-        </is>
-      </c>
-      <c r="X40" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y40" s="4" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z40" s="4" t="inlineStr">
-        <is>
-          <t>class action</t>
-        </is>
-      </c>
-      <c r="AA40" s="4" t="inlineStr"/>
-      <c r="AB40" s="4" t="inlineStr"/>
-      <c r="AC40" s="4" t="inlineStr">
-        <is>
-          <t>3d5db05467b8c673cc133597</t>
-        </is>
-      </c>
-      <c r="AD40" s="4" t="inlineStr">
-        <is>
-          <t>23143c5a5dd4c31fa03783dd</t>
-        </is>
-      </c>
-      <c r="AE40" s="4" t="inlineStr"/>
-      <c r="AF40" s="4" t="inlineStr"/>
-      <c r="AG40" s="4" t="inlineStr"/>
-      <c r="AH40" s="4" t="inlineStr"/>
-      <c r="AI40" s="4" t="inlineStr"/>
-      <c r="AJ40" s="4" t="inlineStr"/>
-      <c r="AK40" s="4" t="inlineStr"/>
-      <c r="AL40" s="4" t="inlineStr"/>
-      <c r="AM40" s="4" t="inlineStr"/>
-      <c r="AN40" s="4" t="inlineStr"/>
-      <c r="AO40" s="4" t="inlineStr"/>
-      <c r="AP40" s="4" t="inlineStr"/>
-      <c r="AQ40" s="4" t="inlineStr"/>
-      <c r="AR40" s="4" t="inlineStr"/>
-      <c r="AS40" s="4" t="inlineStr"/>
-      <c r="AT40" s="4" t="inlineStr"/>
-      <c r="AU40" s="4" t="inlineStr"/>
-      <c r="AV40" s="4" t="inlineStr"/>
-      <c r="AW40" s="4" t="inlineStr"/>
-      <c r="AX40" s="4" t="inlineStr"/>
-      <c r="AY40" s="4" t="inlineStr"/>
-      <c r="AZ40" s="4" t="inlineStr"/>
-      <c r="BA40" s="4" t="inlineStr"/>
-      <c r="BB40" s="4" t="inlineStr">
+      <c r="AP40" s="2" t="inlineStr"/>
+      <c r="AQ40" s="2" t="inlineStr"/>
+      <c r="AR40" s="2" t="inlineStr"/>
+      <c r="AS40" s="2" t="inlineStr"/>
+      <c r="AT40" s="2" t="inlineStr"/>
+      <c r="AU40" s="2" t="inlineStr"/>
+      <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" s="2" t="inlineStr"/>
+      <c r="AX40" s="2" t="inlineStr"/>
+      <c r="AY40" s="2" t="inlineStr"/>
+      <c r="AZ40" s="2" t="inlineStr"/>
+      <c r="BA40" s="2" t="inlineStr"/>
+      <c r="BB40" s="2" t="inlineStr">
         <is>
           <t>COF</t>
         </is>
       </c>
-      <c r="BC40" s="4" t="inlineStr">
+      <c r="BC40" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD40" s="4" t="inlineStr"/>
-      <c r="BE40" s="4" t="inlineStr">
+      <c r="BD40" s="2" t="inlineStr"/>
+      <c r="BE40" s="2" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF40" s="4" t="inlineStr"/>
-      <c r="BG40" s="4" t="inlineStr">
+      <c r="BF40" s="2" t="inlineStr"/>
+      <c r="BG40" s="2" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH40" s="4" t="inlineStr"/>
+      <c r="BH40" s="2" t="inlineStr"/>
+      <c r="BI40" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ40" s="2" t="inlineStr"/>
+      <c r="BK40" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL40" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7693,6 +7989,10 @@
         </is>
       </c>
       <c r="BH41" s="2" t="inlineStr"/>
+      <c r="BI41" s="2" t="inlineStr"/>
+      <c r="BJ41" s="2" t="inlineStr"/>
+      <c r="BK41" s="2" t="inlineStr"/>
+      <c r="BL41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
@@ -7867,6 +8167,10 @@
         </is>
       </c>
       <c r="BH42" s="3" t="inlineStr"/>
+      <c r="BI42" s="3" t="inlineStr"/>
+      <c r="BJ42" s="3" t="inlineStr"/>
+      <c r="BK42" s="3" t="inlineStr"/>
+      <c r="BL42" s="3" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8033,6 +8337,10 @@
         </is>
       </c>
       <c r="BH43" s="2" t="inlineStr"/>
+      <c r="BI43" s="2" t="inlineStr"/>
+      <c r="BJ43" s="2" t="inlineStr"/>
+      <c r="BK43" s="2" t="inlineStr"/>
+      <c r="BL43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -8199,6 +8507,10 @@
       <c r="BF44" s="3" t="inlineStr"/>
       <c r="BG44" s="3" t="inlineStr"/>
       <c r="BH44" s="3" t="inlineStr"/>
+      <c r="BI44" s="3" t="inlineStr"/>
+      <c r="BJ44" s="3" t="inlineStr"/>
+      <c r="BK44" s="3" t="inlineStr"/>
+      <c r="BL44" s="3" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8373,6 +8685,10 @@
       </c>
       <c r="BG45" s="2" t="inlineStr"/>
       <c r="BH45" s="2" t="inlineStr"/>
+      <c r="BI45" s="2" t="inlineStr"/>
+      <c r="BJ45" s="2" t="inlineStr"/>
+      <c r="BK45" s="2" t="inlineStr"/>
+      <c r="BL45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
@@ -8423,13 +8739,17 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L46" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L46" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M46" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N46" s="4" t="inlineStr">
@@ -8482,7 +8802,11 @@
         </is>
       </c>
       <c r="AA46" s="4" t="inlineStr"/>
-      <c r="AB46" s="4" t="inlineStr"/>
+      <c r="AB46" s="4" t="inlineStr">
+        <is>
+          <t>8fa0fbc77f66484d8e01212a7bb6f7e5</t>
+        </is>
+      </c>
       <c r="AC46" s="4" t="inlineStr">
         <is>
           <t>512a755fb4b14ed650b4bb48</t>
@@ -8503,7 +8827,11 @@
       <c r="AL46" s="4" t="inlineStr"/>
       <c r="AM46" s="4" t="inlineStr"/>
       <c r="AN46" s="4" t="inlineStr"/>
-      <c r="AO46" s="4" t="inlineStr"/>
+      <c r="AO46" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP46" s="4" t="inlineStr"/>
       <c r="AQ46" s="4" t="inlineStr"/>
       <c r="AR46" s="4" t="inlineStr"/>
@@ -8547,172 +8875,204 @@
         </is>
       </c>
       <c r="BH46" s="4" t="inlineStr"/>
+      <c r="BI46" s="4" t="inlineStr"/>
+      <c r="BJ46" s="4" t="inlineStr"/>
+      <c r="BK46" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL46" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr"/>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr"/>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Costco</t>
         </is>
       </c>
-      <c r="E47" s="5" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>2026-08-17T02:15:18+08:00</t>
         </is>
       </c>
-      <c r="F47" s="5" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>The mistake that helped cost Rebel Creamery $23.8 million and pushed it into bankruptcy</t>
         </is>
       </c>
-      <c r="G47" s="5" t="inlineStr"/>
-      <c r="H47" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I47" s="5" t="inlineStr">
-        <is>
-          <t>破產</t>
-        </is>
-      </c>
-      <c r="J47" s="5" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K47" s="5" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L47" s="5" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M47" s="5" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>'-0.919</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr"/>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr">
+        <is>
+          <t>主體證據不足</t>
+        </is>
+      </c>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPWHJRcURURXlZbXZUVGUwczZYWnBoSGs1SGZEdFRHVEw5NTU0alRoTElPQkd6bnMwMkUzUzQ5emVFMlhYMlNTaWhzUVBfM3pFV1lWV1otV0lLQ2E1ZnZMWG1yYVZSVlJzTGRHdmpIQ3ZiSWF2dDRTYVRhZHdCRXVQcWdrNGt2UnlLbDBTWjY5dWtyMXBLaU95YVp0RUdUQzlibVdjNktLNmZIaUxpSVg2LWFlV1VKUjJPQXlQV1VpcU10R2Y2ZzlpUWtaWW9lcTJ5ZGZDWQ?oc=5</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>這一錯誤導致 Rebel Creamery 損失 2,380 萬美元，並導致其破產</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>FINANCIAL</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>bankruptcy</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr"/>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>6dd330b498b943ca9c8127905f775078</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>64a7f574d8b47e024826c657</t>
+        </is>
+      </c>
+      <c r="AD47" s="2" t="inlineStr">
+        <is>
+          <t>4b684ac9d5af90e4b5ffdda5</t>
+        </is>
+      </c>
+      <c r="AE47" s="2" t="inlineStr"/>
+      <c r="AF47" s="2" t="inlineStr"/>
+      <c r="AG47" s="2" t="inlineStr"/>
+      <c r="AH47" s="2" t="inlineStr"/>
+      <c r="AI47" s="2" t="inlineStr"/>
+      <c r="AJ47" s="2" t="inlineStr"/>
+      <c r="AK47" s="2" t="inlineStr"/>
+      <c r="AL47" s="2" t="inlineStr"/>
+      <c r="AM47" s="2" t="inlineStr"/>
+      <c r="AN47" s="2" t="inlineStr"/>
+      <c r="AO47" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N47" s="5" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O47" s="5" t="inlineStr">
-        <is>
-          <t>'-0.919</t>
-        </is>
-      </c>
-      <c r="P47" s="5" t="inlineStr"/>
-      <c r="Q47" s="5" t="inlineStr"/>
-      <c r="R47" s="5" t="inlineStr"/>
-      <c r="S47" s="5" t="inlineStr"/>
-      <c r="T47" s="5" t="inlineStr">
+      <c r="AP47" s="2" t="inlineStr"/>
+      <c r="AQ47" s="2" t="inlineStr"/>
+      <c r="AR47" s="2" t="inlineStr"/>
+      <c r="AS47" s="2" t="inlineStr"/>
+      <c r="AT47" s="2" t="inlineStr"/>
+      <c r="AU47" s="2" t="inlineStr"/>
+      <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" s="2" t="inlineStr"/>
+      <c r="AX47" s="2" t="inlineStr"/>
+      <c r="AY47" s="2" t="inlineStr"/>
+      <c r="AZ47" s="2" t="inlineStr"/>
+      <c r="BA47" s="2" t="inlineStr"/>
+      <c r="BB47" s="2" t="inlineStr">
+        <is>
+          <t>COST</t>
+        </is>
+      </c>
+      <c r="BC47" s="2" t="inlineStr">
         <is>
           <t>主體證據不足</t>
         </is>
       </c>
-      <c r="U47" s="5" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPWHJRcURURXlZbXZUVGUwczZYWnBoSGs1SGZEdFRHVEw5NTU0alRoTElPQkd6bnMwMkUzUzQ5emVFMlhYMlNTaWhzUVBfM3pFV1lWV1otV0lLQ2E1ZnZMWG1yYVZSVlJzTGRHdmpIQ3ZiSWF2dDRTYVRhZHdCRXVQcWdrNGt2UnlLbDBTWjY5dWtyMXBLaU95YVp0RUdUQzlibVdjNktLNmZIaUxpSVg2LWFlV1VKUjJPQXlQV1VpcU10R2Y2ZzlpUWtaWW9lcTJ5ZGZDWQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V47" s="5" t="inlineStr">
-        <is>
-          <t>Yahoo</t>
-        </is>
-      </c>
-      <c r="W47" s="5" t="inlineStr">
-        <is>
-          <t>這一錯誤導致 Rebel Creamery 損失 2,380 萬美元，並導致其破產</t>
-        </is>
-      </c>
-      <c r="X47" s="5" t="inlineStr">
-        <is>
-          <t>FINANCIAL</t>
-        </is>
-      </c>
-      <c r="Y47" s="5" t="inlineStr">
-        <is>
-          <t>BANKRUPTCY</t>
-        </is>
-      </c>
-      <c r="Z47" s="5" t="inlineStr">
-        <is>
-          <t>bankruptcy</t>
-        </is>
-      </c>
-      <c r="AA47" s="5" t="inlineStr"/>
-      <c r="AB47" s="5" t="inlineStr"/>
-      <c r="AC47" s="5" t="inlineStr">
-        <is>
-          <t>64a7f574d8b47e024826c657</t>
-        </is>
-      </c>
-      <c r="AD47" s="5" t="inlineStr">
-        <is>
-          <t>4b684ac9d5af90e4b5ffdda5</t>
-        </is>
-      </c>
-      <c r="AE47" s="5" t="inlineStr"/>
-      <c r="AF47" s="5" t="inlineStr"/>
-      <c r="AG47" s="5" t="inlineStr"/>
-      <c r="AH47" s="5" t="inlineStr"/>
-      <c r="AI47" s="5" t="inlineStr"/>
-      <c r="AJ47" s="5" t="inlineStr"/>
-      <c r="AK47" s="5" t="inlineStr"/>
-      <c r="AL47" s="5" t="inlineStr"/>
-      <c r="AM47" s="5" t="inlineStr"/>
-      <c r="AN47" s="5" t="inlineStr"/>
-      <c r="AO47" s="5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP47" s="5" t="inlineStr"/>
-      <c r="AQ47" s="5" t="inlineStr"/>
-      <c r="AR47" s="5" t="inlineStr"/>
-      <c r="AS47" s="5" t="inlineStr"/>
-      <c r="AT47" s="5" t="inlineStr"/>
-      <c r="AU47" s="5" t="inlineStr"/>
-      <c r="AV47" s="5" t="inlineStr"/>
-      <c r="AW47" s="5" t="inlineStr"/>
-      <c r="AX47" s="5" t="inlineStr"/>
-      <c r="AY47" s="5" t="inlineStr"/>
-      <c r="AZ47" s="5" t="inlineStr"/>
-      <c r="BA47" s="5" t="inlineStr"/>
-      <c r="BB47" s="5" t="inlineStr">
+      <c r="BD47" s="2" t="inlineStr">
         <is>
           <t>COST</t>
         </is>
       </c>
-      <c r="BC47" s="5" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD47" s="5" t="inlineStr">
-        <is>
-          <t>COST</t>
-        </is>
-      </c>
-      <c r="BE47" s="5" t="inlineStr"/>
-      <c r="BF47" s="5" t="inlineStr"/>
-      <c r="BG47" s="5" t="inlineStr"/>
-      <c r="BH47" s="5" t="inlineStr"/>
+      <c r="BE47" s="2" t="inlineStr"/>
+      <c r="BF47" s="2" t="inlineStr"/>
+      <c r="BG47" s="2" t="inlineStr"/>
+      <c r="BH47" s="2" t="inlineStr"/>
+      <c r="BI47" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ47" s="2" t="inlineStr"/>
+      <c r="BK47" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL47" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:43:17.016263+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8879,6 +9239,10 @@
         </is>
       </c>
       <c r="BH48" s="2" t="inlineStr"/>
+      <c r="BI48" s="2" t="inlineStr"/>
+      <c r="BJ48" s="2" t="inlineStr"/>
+      <c r="BK48" s="2" t="inlineStr"/>
+      <c r="BL48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9053,6 +9417,10 @@
         </is>
       </c>
       <c r="BH49" s="2" t="inlineStr"/>
+      <c r="BI49" s="2" t="inlineStr"/>
+      <c r="BJ49" s="2" t="inlineStr"/>
+      <c r="BK49" s="2" t="inlineStr"/>
+      <c r="BL49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9227,6 +9595,10 @@
       </c>
       <c r="BG50" s="2" t="inlineStr"/>
       <c r="BH50" s="2" t="inlineStr"/>
+      <c r="BI50" s="2" t="inlineStr"/>
+      <c r="BJ50" s="2" t="inlineStr"/>
+      <c r="BK50" s="2" t="inlineStr"/>
+      <c r="BL50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9393,6 +9765,10 @@
       <c r="BF51" s="2" t="inlineStr"/>
       <c r="BG51" s="2" t="inlineStr"/>
       <c r="BH51" s="2" t="inlineStr"/>
+      <c r="BI51" s="2" t="inlineStr"/>
+      <c r="BJ51" s="2" t="inlineStr"/>
+      <c r="BK51" s="2" t="inlineStr"/>
+      <c r="BL51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9567,6 +9943,10 @@
         </is>
       </c>
       <c r="BH52" s="2" t="inlineStr"/>
+      <c r="BI52" s="2" t="inlineStr"/>
+      <c r="BJ52" s="2" t="inlineStr"/>
+      <c r="BK52" s="2" t="inlineStr"/>
+      <c r="BL52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9741,6 +10121,10 @@
       </c>
       <c r="BG53" s="2" t="inlineStr"/>
       <c r="BH53" s="2" t="inlineStr"/>
+      <c r="BI53" s="2" t="inlineStr"/>
+      <c r="BJ53" s="2" t="inlineStr"/>
+      <c r="BK53" s="2" t="inlineStr"/>
+      <c r="BL53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
@@ -9791,13 +10175,17 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L54" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L54" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M54" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N54" s="4" t="inlineStr">
@@ -9850,7 +10238,11 @@
         </is>
       </c>
       <c r="AA54" s="4" t="inlineStr"/>
-      <c r="AB54" s="4" t="inlineStr"/>
+      <c r="AB54" s="4" t="inlineStr">
+        <is>
+          <t>6713211c171648ac98b1f671167a39f4</t>
+        </is>
+      </c>
       <c r="AC54" s="4" t="inlineStr">
         <is>
           <t>a929e326ef866bb2058da1eb</t>
@@ -9871,7 +10263,11 @@
       <c r="AL54" s="4" t="inlineStr"/>
       <c r="AM54" s="4" t="inlineStr"/>
       <c r="AN54" s="4" t="inlineStr"/>
-      <c r="AO54" s="4" t="inlineStr"/>
+      <c r="AO54" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP54" s="4" t="inlineStr"/>
       <c r="AQ54" s="4" t="inlineStr"/>
       <c r="AR54" s="4" t="inlineStr"/>
@@ -9907,6 +10303,18 @@
         </is>
       </c>
       <c r="BH54" s="4" t="inlineStr"/>
+      <c r="BI54" s="4" t="inlineStr"/>
+      <c r="BJ54" s="4" t="inlineStr"/>
+      <c r="BK54" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL54" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
@@ -9957,13 +10365,17 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L55" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L55" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M55" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N55" s="4" t="inlineStr">
@@ -10016,7 +10428,11 @@
         </is>
       </c>
       <c r="AA55" s="4" t="inlineStr"/>
-      <c r="AB55" s="4" t="inlineStr"/>
+      <c r="AB55" s="4" t="inlineStr">
+        <is>
+          <t>e313433dc1f8469b955af6cc5a1e31b9</t>
+        </is>
+      </c>
       <c r="AC55" s="4" t="inlineStr">
         <is>
           <t>fe41888492b6b722215454c3</t>
@@ -10037,7 +10453,11 @@
       <c r="AL55" s="4" t="inlineStr"/>
       <c r="AM55" s="4" t="inlineStr"/>
       <c r="AN55" s="4" t="inlineStr"/>
-      <c r="AO55" s="4" t="inlineStr"/>
+      <c r="AO55" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP55" s="4" t="inlineStr"/>
       <c r="AQ55" s="4" t="inlineStr"/>
       <c r="AR55" s="4" t="inlineStr"/>
@@ -10081,9 +10501,21 @@
         </is>
       </c>
       <c r="BH55" s="4" t="inlineStr"/>
+      <c r="BI55" s="4" t="inlineStr"/>
+      <c r="BJ55" s="4" t="inlineStr"/>
+      <c r="BK55" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL55" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH55"/>
+  <autoFilter ref="A1:BL55"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10094,7 +10526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH28"/>
+  <dimension ref="A1:BL24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -10157,6 +10589,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10458,6 +10894,26 @@
       <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Ticker稽核警示</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
         </is>
       </c>
     </row>
@@ -10634,6 +11090,10 @@
         </is>
       </c>
       <c r="BH2" s="3" t="inlineStr"/>
+      <c r="BI2" s="3" t="inlineStr"/>
+      <c r="BJ2" s="3" t="inlineStr"/>
+      <c r="BK2" s="3" t="inlineStr"/>
+      <c r="BL2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -10800,6 +11260,10 @@
         </is>
       </c>
       <c r="BH3" s="3" t="inlineStr"/>
+      <c r="BI3" s="3" t="inlineStr"/>
+      <c r="BJ3" s="3" t="inlineStr"/>
+      <c r="BK3" s="3" t="inlineStr"/>
+      <c r="BL3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -10974,6 +11438,10 @@
         </is>
       </c>
       <c r="BH4" s="3" t="inlineStr"/>
+      <c r="BI4" s="3" t="inlineStr"/>
+      <c r="BJ4" s="3" t="inlineStr"/>
+      <c r="BK4" s="3" t="inlineStr"/>
+      <c r="BL4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -11148,6 +11616,10 @@
         </is>
       </c>
       <c r="BH5" s="3" t="inlineStr"/>
+      <c r="BI5" s="3" t="inlineStr"/>
+      <c r="BJ5" s="3" t="inlineStr"/>
+      <c r="BK5" s="3" t="inlineStr"/>
+      <c r="BL5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -11314,6 +11786,10 @@
       <c r="BF6" s="3" t="inlineStr"/>
       <c r="BG6" s="3" t="inlineStr"/>
       <c r="BH6" s="3" t="inlineStr"/>
+      <c r="BI6" s="3" t="inlineStr"/>
+      <c r="BJ6" s="3" t="inlineStr"/>
+      <c r="BK6" s="3" t="inlineStr"/>
+      <c r="BL6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -11364,13 +11840,17 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
@@ -11423,7 +11903,11 @@
         </is>
       </c>
       <c r="AA7" s="4" t="inlineStr"/>
-      <c r="AB7" s="4" t="inlineStr"/>
+      <c r="AB7" s="4" t="inlineStr">
+        <is>
+          <t>95e5975c26d94c3982698dda68748d10</t>
+        </is>
+      </c>
       <c r="AC7" s="4" t="inlineStr">
         <is>
           <t>b533b8bea98bf27fa55b6f81</t>
@@ -11444,7 +11928,11 @@
       <c r="AL7" s="4" t="inlineStr"/>
       <c r="AM7" s="4" t="inlineStr"/>
       <c r="AN7" s="4" t="inlineStr"/>
-      <c r="AO7" s="4" t="inlineStr"/>
+      <c r="AO7" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP7" s="4" t="inlineStr"/>
       <c r="AQ7" s="4" t="inlineStr"/>
       <c r="AR7" s="4" t="inlineStr"/>
@@ -11488,6 +11976,18 @@
         </is>
       </c>
       <c r="BH7" s="4" t="inlineStr"/>
+      <c r="BI7" s="4" t="inlineStr"/>
+      <c r="BJ7" s="4" t="inlineStr"/>
+      <c r="BK7" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -11662,6 +12162,10 @@
         </is>
       </c>
       <c r="BH8" s="3" t="inlineStr"/>
+      <c r="BI8" s="3" t="inlineStr"/>
+      <c r="BJ8" s="3" t="inlineStr"/>
+      <c r="BK8" s="3" t="inlineStr"/>
+      <c r="BL8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -11836,6 +12340,10 @@
       </c>
       <c r="BG9" s="3" t="inlineStr"/>
       <c r="BH9" s="3" t="inlineStr"/>
+      <c r="BI9" s="3" t="inlineStr"/>
+      <c r="BJ9" s="3" t="inlineStr"/>
+      <c r="BK9" s="3" t="inlineStr"/>
+      <c r="BL9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -12010,6 +12518,10 @@
         </is>
       </c>
       <c r="BH10" s="3" t="inlineStr"/>
+      <c r="BI10" s="3" t="inlineStr"/>
+      <c r="BJ10" s="3" t="inlineStr"/>
+      <c r="BK10" s="3" t="inlineStr"/>
+      <c r="BL10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -12184,6 +12696,10 @@
         </is>
       </c>
       <c r="BH11" s="3" t="inlineStr"/>
+      <c r="BI11" s="3" t="inlineStr"/>
+      <c r="BJ11" s="3" t="inlineStr"/>
+      <c r="BK11" s="3" t="inlineStr"/>
+      <c r="BL11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -12350,6 +12866,10 @@
         </is>
       </c>
       <c r="BH12" s="3" t="inlineStr"/>
+      <c r="BI12" s="3" t="inlineStr"/>
+      <c r="BJ12" s="3" t="inlineStr"/>
+      <c r="BK12" s="3" t="inlineStr"/>
+      <c r="BL12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -12516,6 +13036,10 @@
       <c r="BF13" s="3" t="inlineStr"/>
       <c r="BG13" s="3" t="inlineStr"/>
       <c r="BH13" s="3" t="inlineStr"/>
+      <c r="BI13" s="3" t="inlineStr"/>
+      <c r="BJ13" s="3" t="inlineStr"/>
+      <c r="BK13" s="3" t="inlineStr"/>
+      <c r="BL13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -12690,6 +13214,10 @@
         </is>
       </c>
       <c r="BH14" s="3" t="inlineStr"/>
+      <c r="BI14" s="3" t="inlineStr"/>
+      <c r="BJ14" s="3" t="inlineStr"/>
+      <c r="BK14" s="3" t="inlineStr"/>
+      <c r="BL14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -12864,6 +13392,10 @@
         </is>
       </c>
       <c r="BH15" s="3" t="inlineStr"/>
+      <c r="BI15" s="3" t="inlineStr"/>
+      <c r="BJ15" s="3" t="inlineStr"/>
+      <c r="BK15" s="3" t="inlineStr"/>
+      <c r="BL15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -13038,6 +13570,10 @@
         </is>
       </c>
       <c r="BH16" s="3" t="inlineStr"/>
+      <c r="BI16" s="3" t="inlineStr"/>
+      <c r="BJ16" s="3" t="inlineStr"/>
+      <c r="BK16" s="3" t="inlineStr"/>
+      <c r="BL16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -13212,6 +13748,10 @@
       </c>
       <c r="BG17" s="3" t="inlineStr"/>
       <c r="BH17" s="3" t="inlineStr"/>
+      <c r="BI17" s="3" t="inlineStr"/>
+      <c r="BJ17" s="3" t="inlineStr"/>
+      <c r="BK17" s="3" t="inlineStr"/>
+      <c r="BL17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -13262,13 +13802,17 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L18" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N18" s="4" t="inlineStr">
@@ -13321,7 +13865,11 @@
         </is>
       </c>
       <c r="AA18" s="4" t="inlineStr"/>
-      <c r="AB18" s="4" t="inlineStr"/>
+      <c r="AB18" s="4" t="inlineStr">
+        <is>
+          <t>d023b0eb009747c18a67f1444cb80104</t>
+        </is>
+      </c>
       <c r="AC18" s="4" t="inlineStr">
         <is>
           <t>9fc0c06395e11a1f12ce636d</t>
@@ -13342,7 +13890,11 @@
       <c r="AL18" s="4" t="inlineStr"/>
       <c r="AM18" s="4" t="inlineStr"/>
       <c r="AN18" s="4" t="inlineStr"/>
-      <c r="AO18" s="4" t="inlineStr"/>
+      <c r="AO18" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP18" s="4" t="inlineStr"/>
       <c r="AQ18" s="4" t="inlineStr"/>
       <c r="AR18" s="4" t="inlineStr"/>
@@ -13386,6 +13938,18 @@
         </is>
       </c>
       <c r="BH18" s="4" t="inlineStr"/>
+      <c r="BI18" s="4" t="inlineStr"/>
+      <c r="BJ18" s="4" t="inlineStr"/>
+      <c r="BK18" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL18" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -13436,13 +14000,17 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L19" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N19" s="4" t="inlineStr">
@@ -13495,7 +14063,11 @@
         </is>
       </c>
       <c r="AA19" s="4" t="inlineStr"/>
-      <c r="AB19" s="4" t="inlineStr"/>
+      <c r="AB19" s="4" t="inlineStr">
+        <is>
+          <t>033742cfa14a4dc7a0f036c3839ff9c8</t>
+        </is>
+      </c>
       <c r="AC19" s="4" t="inlineStr">
         <is>
           <t>eab8ed09444f99fbe8f3f632</t>
@@ -13516,7 +14088,11 @@
       <c r="AL19" s="4" t="inlineStr"/>
       <c r="AM19" s="4" t="inlineStr"/>
       <c r="AN19" s="4" t="inlineStr"/>
-      <c r="AO19" s="4" t="inlineStr"/>
+      <c r="AO19" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP19" s="4" t="inlineStr"/>
       <c r="AQ19" s="4" t="inlineStr"/>
       <c r="AR19" s="4" t="inlineStr"/>
@@ -13552,354 +14128,366 @@
         </is>
       </c>
       <c r="BH19" s="4" t="inlineStr"/>
+      <c r="BI19" s="4" t="inlineStr"/>
+      <c r="BJ19" s="4" t="inlineStr"/>
+      <c r="BK19" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL19" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>WMT</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>Walmart Inc.</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-17T05:12:05+08:00</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>Popular ice cream brand sold at Walmart and Target files for bankruptcy</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr"/>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I20" s="5" t="inlineStr">
-        <is>
-          <t>破產</t>
-        </is>
-      </c>
-      <c r="J20" s="5" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K20" s="5" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>FDX</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>FedEx Corporation Common Stock</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-17T04:00:00+08:00</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>2026 St. Jude Championship TV schedule, coverage: Where to watch first leg of FedEx Cup Playoffs</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>裁員或人力縮減</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L20" s="5" t="inlineStr"/>
-      <c r="M20" s="5" t="inlineStr">
+      <c r="L20" s="3" t="inlineStr"/>
+      <c r="M20" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N20" s="5" t="inlineStr">
+      <c r="N20" s="3" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O20" s="5" t="inlineStr">
-        <is>
-          <t>'-0.757</t>
-        </is>
-      </c>
-      <c r="P20" s="5" t="inlineStr"/>
-      <c r="Q20" s="5" t="inlineStr"/>
-      <c r="R20" s="5" t="inlineStr"/>
-      <c r="S20" s="5" t="inlineStr"/>
-      <c r="T20" s="5" t="inlineStr">
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>'-0.006</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr"/>
+      <c r="Q20" s="3" t="inlineStr"/>
+      <c r="R20" s="3" t="inlineStr"/>
+      <c r="S20" s="3" t="inlineStr"/>
+      <c r="T20" s="3" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U20" s="5" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQZ2NOcHBBeFgwamJCQ0hNWmJkLXJHOTZjUU5aT1hVOEpfSzY1aW8wZ2NLMFVYNE5QZG5zLUxMTGYzWUQzLTV1SDJXbkRuZnJoWW92R250WmpMaXZEZFFHajBqU2Q2NG44aU1qX2hUOVdyZnhsQlYxeTVrakhOYTZyT3kzaWpNUGRWLWZ4andORUJrMm9nVzk0bQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V20" s="5" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W20" s="5" t="inlineStr">
-        <is>
-          <t>沃爾瑪和塔吉特銷售的熱門冰淇淋品牌申請破產</t>
-        </is>
-      </c>
-      <c r="X20" s="5" t="inlineStr">
-        <is>
-          <t>FINANCIAL</t>
-        </is>
-      </c>
-      <c r="Y20" s="5" t="inlineStr">
-        <is>
-          <t>BANKRUPTCY</t>
-        </is>
-      </c>
-      <c r="Z20" s="5" t="inlineStr">
-        <is>
-          <t>bankruptcy</t>
-        </is>
-      </c>
-      <c r="AA20" s="5" t="inlineStr"/>
-      <c r="AB20" s="5" t="inlineStr"/>
-      <c r="AC20" s="5" t="inlineStr">
-        <is>
-          <t>35a1e5ff35be561beca55240</t>
-        </is>
-      </c>
-      <c r="AD20" s="5" t="inlineStr">
-        <is>
-          <t>101a5c0eec5ff35f912347c8</t>
-        </is>
-      </c>
-      <c r="AE20" s="5" t="inlineStr"/>
-      <c r="AF20" s="5" t="inlineStr"/>
-      <c r="AG20" s="5" t="inlineStr"/>
-      <c r="AH20" s="5" t="inlineStr"/>
-      <c r="AI20" s="5" t="inlineStr"/>
-      <c r="AJ20" s="5" t="inlineStr"/>
-      <c r="AK20" s="5" t="inlineStr"/>
-      <c r="AL20" s="5" t="inlineStr"/>
-      <c r="AM20" s="5" t="inlineStr"/>
-      <c r="AN20" s="5" t="inlineStr"/>
-      <c r="AO20" s="5" t="inlineStr"/>
-      <c r="AP20" s="5" t="inlineStr"/>
-      <c r="AQ20" s="5" t="inlineStr"/>
-      <c r="AR20" s="5" t="inlineStr"/>
-      <c r="AS20" s="5" t="inlineStr"/>
-      <c r="AT20" s="5" t="inlineStr"/>
-      <c r="AU20" s="5" t="inlineStr"/>
-      <c r="AV20" s="5" t="inlineStr"/>
-      <c r="AW20" s="5" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="AX20" s="5" t="inlineStr"/>
-      <c r="AY20" s="5" t="inlineStr"/>
-      <c r="AZ20" s="5" t="inlineStr"/>
-      <c r="BA20" s="5" t="inlineStr"/>
-      <c r="BB20" s="5" t="inlineStr">
-        <is>
-          <t>WMT</t>
-        </is>
-      </c>
-      <c r="BC20" s="5" t="inlineStr">
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQOHkxSGVRQzdhLUtGMl9CQWlLM05OVklfYk5hXzczZ0I2ajVfUl9RcDhkX19MLWhfWTVENHJmR19yXzZaNXVmZDQ5UGRUVldxNnVHTUpYM1BpUVNScXhzNmJxaENzNm96WkFqOXNpZkFYSjB2bFJ2eDdtM1lMSFBHWW96MU9zRDhmZm5XNEpGR1NWRHJJUk1DdF9nVzNBVVBIOW5fWU1lV2F6dzhUdTZxaE1XbWstZXBKZ3BFVkJoWkJGMUNQRkE?oc=5</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
+          <t>CBS Sports</t>
+        </is>
+      </c>
+      <c r="W20" s="3" t="inlineStr">
+        <is>
+          <t>2026 年聖裘德錦標賽電視節目表、報導：在哪裡觀看聯邦快遞杯季後賽第一回合</t>
+        </is>
+      </c>
+      <c r="X20" s="3" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y20" s="3" t="inlineStr">
+        <is>
+          <t>WORKFORCE_REDUCTION</t>
+        </is>
+      </c>
+      <c r="Z20" s="3" t="inlineStr">
+        <is>
+          <t>layoff；layoffs</t>
+        </is>
+      </c>
+      <c r="AA20" s="3" t="inlineStr"/>
+      <c r="AB20" s="3" t="inlineStr"/>
+      <c r="AC20" s="3" t="inlineStr">
+        <is>
+          <t>45e067ff7b8f7136b37e5f84</t>
+        </is>
+      </c>
+      <c r="AD20" s="3" t="inlineStr">
+        <is>
+          <t>c71ad688d3fa04a21868e114</t>
+        </is>
+      </c>
+      <c r="AE20" s="3" t="inlineStr"/>
+      <c r="AF20" s="3" t="inlineStr"/>
+      <c r="AG20" s="3" t="inlineStr"/>
+      <c r="AH20" s="3" t="inlineStr"/>
+      <c r="AI20" s="3" t="inlineStr"/>
+      <c r="AJ20" s="3" t="inlineStr"/>
+      <c r="AK20" s="3" t="inlineStr"/>
+      <c r="AL20" s="3" t="inlineStr"/>
+      <c r="AM20" s="3" t="inlineStr"/>
+      <c r="AN20" s="3" t="inlineStr"/>
+      <c r="AO20" s="3" t="inlineStr"/>
+      <c r="AP20" s="3" t="inlineStr"/>
+      <c r="AQ20" s="3" t="inlineStr"/>
+      <c r="AR20" s="3" t="inlineStr"/>
+      <c r="AS20" s="3" t="inlineStr"/>
+      <c r="AT20" s="3" t="inlineStr"/>
+      <c r="AU20" s="3" t="inlineStr"/>
+      <c r="AV20" s="3" t="inlineStr"/>
+      <c r="AW20" s="3" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="AX20" s="3" t="inlineStr"/>
+      <c r="AY20" s="3" t="inlineStr"/>
+      <c r="AZ20" s="3" t="inlineStr"/>
+      <c r="BA20" s="3" t="inlineStr"/>
+      <c r="BB20" s="3" t="inlineStr">
+        <is>
+          <t>FDX</t>
+        </is>
+      </c>
+      <c r="BC20" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD20" s="5" t="inlineStr"/>
-      <c r="BE20" s="5" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF20" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG20" s="5" t="inlineStr">
+      <c r="BD20" s="3" t="inlineStr"/>
+      <c r="BE20" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF20" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
+      <c r="BG20" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH20" s="5" t="inlineStr"/>
+      <c r="BH20" s="3" t="inlineStr"/>
+      <c r="BI20" s="3" t="inlineStr"/>
+      <c r="BJ20" s="3" t="inlineStr"/>
+      <c r="BK20" s="3" t="inlineStr"/>
+      <c r="BL20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr"/>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>Intercontinental Exchange</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-17T05:12:05+08:00</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>Popular ice cream brand sold at Walmart and Target files for bankruptcy</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr"/>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I21" s="5" t="inlineStr">
-        <is>
-          <t>破產</t>
-        </is>
-      </c>
-      <c r="J21" s="5" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K21" s="5" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr"/>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>General Motors</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-17T03:38:53+08:00</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Aces Vs Liberty Gm 2 | 2024 WNBA Playoffs | WNBA Best Bets &amp; Predictions | ChrisBeCappinn Show Golshifteh Farahani (nfYEvsTvq9)</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>裁員或人力縮減</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L21" s="5" t="inlineStr">
+      <c r="L21" s="3" t="inlineStr">
         <is>
           <t>待人工覆核</t>
         </is>
       </c>
-      <c r="M21" s="5" t="inlineStr">
+      <c r="M21" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N21" s="5" t="inlineStr">
+      <c r="N21" s="3" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O21" s="5" t="inlineStr">
-        <is>
-          <t>'-0.757</t>
-        </is>
-      </c>
-      <c r="P21" s="5" t="inlineStr"/>
-      <c r="Q21" s="5" t="inlineStr"/>
-      <c r="R21" s="5" t="inlineStr"/>
-      <c r="S21" s="5" t="inlineStr"/>
-      <c r="T21" s="5" t="inlineStr">
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>0.014</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr"/>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr"/>
+      <c r="S21" s="3" t="inlineStr"/>
+      <c r="T21" s="3" t="inlineStr">
         <is>
           <t>主體證據不足</t>
         </is>
       </c>
-      <c r="U21" s="5" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQZ2NOcHBBeFgwamJCQ0hNWmJkLXJHOTZjUU5aT1hVOEpfSzY1aW8wZ2NLMFVYNE5QZG5zLUxMTGYzWUQzLTV1SDJXbkRuZnJoWW92R250WmpMaXZEZFFHajBqU2Q2NG44aU1qX2hUOVdyZnhsQlYxeTVrakhOYTZyT3kzaWpNUGRWLWZ4andORUJrMm9nVzk0bQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V21" s="5" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W21" s="5" t="inlineStr">
-        <is>
-          <t>沃爾瑪和塔吉特銷售的熱門冰淇淋品牌申請破產</t>
-        </is>
-      </c>
-      <c r="X21" s="5" t="inlineStr">
-        <is>
-          <t>FINANCIAL</t>
-        </is>
-      </c>
-      <c r="Y21" s="5" t="inlineStr">
-        <is>
-          <t>BANKRUPTCY</t>
-        </is>
-      </c>
-      <c r="Z21" s="5" t="inlineStr">
-        <is>
-          <t>bankruptcy</t>
-        </is>
-      </c>
-      <c r="AA21" s="5" t="inlineStr"/>
-      <c r="AB21" s="5" t="inlineStr"/>
-      <c r="AC21" s="5" t="inlineStr">
-        <is>
-          <t>35a1e5ff35be561beca55240</t>
-        </is>
-      </c>
-      <c r="AD21" s="5" t="inlineStr">
-        <is>
-          <t>11dfdd497cf6d878e41e446f</t>
-        </is>
-      </c>
-      <c r="AE21" s="5" t="inlineStr"/>
-      <c r="AF21" s="5" t="inlineStr"/>
-      <c r="AG21" s="5" t="inlineStr"/>
-      <c r="AH21" s="5" t="inlineStr"/>
-      <c r="AI21" s="5" t="inlineStr"/>
-      <c r="AJ21" s="5" t="inlineStr"/>
-      <c r="AK21" s="5" t="inlineStr"/>
-      <c r="AL21" s="5" t="inlineStr"/>
-      <c r="AM21" s="5" t="inlineStr"/>
-      <c r="AN21" s="5" t="inlineStr"/>
-      <c r="AO21" s="5" t="inlineStr">
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTFBZLWVvZmg5YXhKZW5OM3hSZU1sNjBRd0RSRXJpRHRwTmZyV2RYelJucG9CMGlFQVhvUWNKdDBxOGNoWFJTWng0NFNZTHdicHYtY3JhVlpSZjBxZWxwR2xMSw?oc=5</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t>Mshale</t>
+        </is>
+      </c>
+      <c r="W21" s="3" t="inlineStr">
+        <is>
+          <t>王牌 vs 自由 Gm 2 | 2024 年 WNBA 季後賽 | WNBA 最佳投注和預測 | ChrisBeCappinn 秀 Golshifteh Farahani (nfYEvsTvq9)</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y21" s="3" t="inlineStr">
+        <is>
+          <t>WORKFORCE_REDUCTION</t>
+        </is>
+      </c>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
+          <t>layoff；layoffs</t>
+        </is>
+      </c>
+      <c r="AA21" s="3" t="inlineStr"/>
+      <c r="AB21" s="3" t="inlineStr"/>
+      <c r="AC21" s="3" t="inlineStr">
+        <is>
+          <t>682c207a9e66b0162d0f8448</t>
+        </is>
+      </c>
+      <c r="AD21" s="3" t="inlineStr">
+        <is>
+          <t>f9f51d4e201987502efdbeb4</t>
+        </is>
+      </c>
+      <c r="AE21" s="3" t="inlineStr"/>
+      <c r="AF21" s="3" t="inlineStr"/>
+      <c r="AG21" s="3" t="inlineStr"/>
+      <c r="AH21" s="3" t="inlineStr"/>
+      <c r="AI21" s="3" t="inlineStr"/>
+      <c r="AJ21" s="3" t="inlineStr"/>
+      <c r="AK21" s="3" t="inlineStr"/>
+      <c r="AL21" s="3" t="inlineStr"/>
+      <c r="AM21" s="3" t="inlineStr"/>
+      <c r="AN21" s="3" t="inlineStr"/>
+      <c r="AO21" s="3" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AP21" s="5" t="inlineStr"/>
-      <c r="AQ21" s="5" t="inlineStr"/>
-      <c r="AR21" s="5" t="inlineStr"/>
-      <c r="AS21" s="5" t="inlineStr"/>
-      <c r="AT21" s="5" t="inlineStr"/>
-      <c r="AU21" s="5" t="inlineStr"/>
-      <c r="AV21" s="5" t="inlineStr"/>
-      <c r="AW21" s="5" t="inlineStr"/>
-      <c r="AX21" s="5" t="inlineStr"/>
-      <c r="AY21" s="5" t="inlineStr"/>
-      <c r="AZ21" s="5" t="inlineStr"/>
-      <c r="BA21" s="5" t="inlineStr"/>
-      <c r="BB21" s="5" t="inlineStr">
-        <is>
-          <t>ICE</t>
-        </is>
-      </c>
-      <c r="BC21" s="5" t="inlineStr">
+      <c r="AP21" s="3" t="inlineStr"/>
+      <c r="AQ21" s="3" t="inlineStr"/>
+      <c r="AR21" s="3" t="inlineStr"/>
+      <c r="AS21" s="3" t="inlineStr"/>
+      <c r="AT21" s="3" t="inlineStr"/>
+      <c r="AU21" s="3" t="inlineStr"/>
+      <c r="AV21" s="3" t="inlineStr"/>
+      <c r="AW21" s="3" t="inlineStr"/>
+      <c r="AX21" s="3" t="inlineStr"/>
+      <c r="AY21" s="3" t="inlineStr"/>
+      <c r="AZ21" s="3" t="inlineStr"/>
+      <c r="BA21" s="3" t="inlineStr"/>
+      <c r="BB21" s="3" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="BC21" s="3" t="inlineStr">
         <is>
           <t>主體證據不足</t>
         </is>
       </c>
-      <c r="BD21" s="5" t="inlineStr">
-        <is>
-          <t>ICE</t>
-        </is>
-      </c>
-      <c r="BE21" s="5" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF21" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG21" s="5" t="inlineStr"/>
-      <c r="BH21" s="5" t="inlineStr"/>
+      <c r="BD21" s="3" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="BE21" s="3" t="inlineStr"/>
+      <c r="BF21" s="3" t="inlineStr"/>
+      <c r="BG21" s="3" t="inlineStr"/>
+      <c r="BH21" s="3" t="inlineStr"/>
+      <c r="BI21" s="3" t="inlineStr"/>
+      <c r="BJ21" s="3" t="inlineStr"/>
+      <c r="BK21" s="3" t="inlineStr"/>
+      <c r="BL21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -13914,22 +14502,22 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>COF</t>
+          <t>PODD</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Insulet Corporation</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T05:06:39+08:00</t>
+          <t>2026-08-17T02:31:00+08:00</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Boy George - Radio Interview (3 Jul 26) Capital One Class Action Lawsuit (61jGcnyHu9)</t>
+          <t>PODD UPCOMING DEADLINE: Faruqi &amp; Faruqi, LLP Reminds Insulet (PODD) Investors of Securities Class Action Lawsuit Deadline on August 31, 2026</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr"/>
@@ -13950,13 +14538,17 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L22" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N22" s="4" t="inlineStr">
@@ -13966,7 +14558,7 @@
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>'-0.232</t>
+          <t>'-0.065</t>
         </is>
       </c>
       <c r="P22" s="4" t="inlineStr"/>
@@ -13980,17 +14572,17 @@
       </c>
       <c r="U22" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTFBsZlRfNXdiVjV3OTFrMGNxM2JOcmVOY2tWQloxeXJuZWJhenJmblc0VC1sOTRkZWxIeEhfNjR0T2tvTmJYLVJDd29HbWczMVkzNWZkUTNjQ2dBTHM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxNZlJ3S0xCR2RwRHY1djNQNnYyX29Vd1YwUXhoNGkzWG1vRkxtck9Oamx3WEFCQUZiQVJWbnZBNFJYTm9fRklCVUpnQTVFb1ZQVVI2QW5sdnVlUmJ2NkdIZHRNc242alowMjFMdDA5ejd6eVZpRDB6X3NBTnpISU1FSUZkWlgyVmc1Y1JZbFFwckFwLTVQbmVTZHpocjZuWkpKaV84elp6R2ZCRXZtcjAxcjMzaVNhREpubldSV0FEVVFCQTJnQWl3N3RiejU5Rlc5bTF4OGdCSTFvaUpSQkRNQW1tam8tX2ZWVURiNkViYVBfUGhMM05oU2RfamdHTjRqSllzUnBPak8?oc=5</t>
         </is>
       </c>
       <c r="V22" s="4" t="inlineStr">
         <is>
-          <t>Mshale</t>
+          <t>TMX Newsfile</t>
         </is>
       </c>
       <c r="W22" s="4" t="inlineStr">
         <is>
-          <t>Boy George - 電台訪談（26 年 7 月 3 日）第一資本集體訴訟 (61jGcnyHu9)</t>
+          <t>PODD 截止日期即將到來：Faruqi &amp; Faruqi, LLP 提醒 Insulet (PODD) 投資者證券集體訴訟截止日期為 2026 年 8 月 31 日</t>
         </is>
       </c>
       <c r="X22" s="4" t="inlineStr">
@@ -14009,15 +14601,19 @@
         </is>
       </c>
       <c r="AA22" s="4" t="inlineStr"/>
-      <c r="AB22" s="4" t="inlineStr"/>
+      <c r="AB22" s="4" t="inlineStr">
+        <is>
+          <t>8fa0fbc77f66484d8e01212a7bb6f7e5</t>
+        </is>
+      </c>
       <c r="AC22" s="4" t="inlineStr">
         <is>
-          <t>3d5db05467b8c673cc133597</t>
+          <t>512a755fb4b14ed650b4bb48</t>
         </is>
       </c>
       <c r="AD22" s="4" t="inlineStr">
         <is>
-          <t>23143c5a5dd4c31fa03783dd</t>
+          <t>b87674e722f99233c85565cf</t>
         </is>
       </c>
       <c r="AE22" s="4" t="inlineStr"/>
@@ -14030,7 +14626,11 @@
       <c r="AL22" s="4" t="inlineStr"/>
       <c r="AM22" s="4" t="inlineStr"/>
       <c r="AN22" s="4" t="inlineStr"/>
-      <c r="AO22" s="4" t="inlineStr"/>
+      <c r="AO22" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP22" s="4" t="inlineStr"/>
       <c r="AQ22" s="4" t="inlineStr"/>
       <c r="AR22" s="4" t="inlineStr"/>
@@ -14038,14 +14638,18 @@
       <c r="AT22" s="4" t="inlineStr"/>
       <c r="AU22" s="4" t="inlineStr"/>
       <c r="AV22" s="4" t="inlineStr"/>
-      <c r="AW22" s="4" t="inlineStr"/>
+      <c r="AW22" s="4" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
       <c r="AX22" s="4" t="inlineStr"/>
       <c r="AY22" s="4" t="inlineStr"/>
       <c r="AZ22" s="4" t="inlineStr"/>
       <c r="BA22" s="4" t="inlineStr"/>
       <c r="BB22" s="4" t="inlineStr">
         <is>
-          <t>COF</t>
+          <t>PODD</t>
         </is>
       </c>
       <c r="BC22" s="4" t="inlineStr">
@@ -14056,1039 +14660,423 @@
       <c r="BD22" s="4" t="inlineStr"/>
       <c r="BE22" s="4" t="inlineStr">
         <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF22" s="4" t="inlineStr"/>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF22" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.654565+00:00</t>
+        </is>
+      </c>
       <c r="BG22" s="4" t="inlineStr">
         <is>
-          <t>公司清單／交易所參照</t>
+          <t>交易所目前名單</t>
         </is>
       </c>
       <c r="BH22" s="4" t="inlineStr"/>
+      <c r="BI22" s="4" t="inlineStr"/>
+      <c r="BJ22" s="4" t="inlineStr"/>
+      <c r="BK22" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL22" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>FDX</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>FedEx Corporation Common Stock</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-17T04:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>2026 St. Jude Championship TV schedule, coverage: Where to watch first leg of FedEx Cup Playoffs</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr"/>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L23" s="3" t="inlineStr"/>
-      <c r="M23" s="3" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>PNR</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Pentair</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-17T01:00:00+08:00</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-16 | PNR STOCKHOLDER ALERT: Bronstein, Gewirtz and Grossman, LLC Announces that Pentair plc Investors with Substantial Losses Have Opportunity to Lead Class Action Lawsuit! | NYSE:PNR | Press Release</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr"/>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>重大訴訟</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M23" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N23" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O23" s="4" t="inlineStr">
+        <is>
+          <t>'-0.7</t>
+        </is>
+      </c>
+      <c r="P23" s="4" t="inlineStr"/>
+      <c r="Q23" s="4" t="inlineStr"/>
+      <c r="R23" s="4" t="inlineStr"/>
+      <c r="S23" s="4" t="inlineStr"/>
+      <c r="T23" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U23" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxOQ1kybWpYemNLWEFXdm9Fc1hnR0pOWkNqWkluSWJFMWtkRmNKMDJLRUs1dk5OeEdWSGY3LUZFUVU1cms2dkJaODZDVTdXQmlWTkxQcFcxTVJtVURVbk5zMUhWdkJaeEFIcFRNcjRQUzl5dWJnTDdjWXdFdWlmWF9pTkJvNngwVVhxUE8xMnlMMnJPUFdWMkVSMWpZaVlRWXppdnNnSVBIcnFJN1F4eFFvcGpfWGtZQ0ptOGdXY3N0VmJ4dFdWX3hFZTNCcjRaUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="V23" s="4" t="inlineStr">
+        <is>
+          <t>Stockhouse</t>
+        </is>
+      </c>
+      <c r="W23" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-16 | PNR 股東提醒：Bronstein、Gewirtz 和 Grossman, LLC 宣布遭受重大損失的 Pentair plc 投資者有機會提起集體訴訟！ |紐約證券交易所：PNR |新聞稿</t>
+        </is>
+      </c>
+      <c r="X23" s="4" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y23" s="4" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z23" s="4" t="inlineStr">
+        <is>
+          <t>class action</t>
+        </is>
+      </c>
+      <c r="AA23" s="4" t="inlineStr"/>
+      <c r="AB23" s="4" t="inlineStr">
+        <is>
+          <t>6713211c171648ac98b1f671167a39f4</t>
+        </is>
+      </c>
+      <c r="AC23" s="4" t="inlineStr">
+        <is>
+          <t>a929e326ef866bb2058da1eb</t>
+        </is>
+      </c>
+      <c r="AD23" s="4" t="inlineStr">
+        <is>
+          <t>ee57266d6e4d6dfd4d68c58c</t>
+        </is>
+      </c>
+      <c r="AE23" s="4" t="inlineStr"/>
+      <c r="AF23" s="4" t="inlineStr"/>
+      <c r="AG23" s="4" t="inlineStr"/>
+      <c r="AH23" s="4" t="inlineStr"/>
+      <c r="AI23" s="4" t="inlineStr"/>
+      <c r="AJ23" s="4" t="inlineStr"/>
+      <c r="AK23" s="4" t="inlineStr"/>
+      <c r="AL23" s="4" t="inlineStr"/>
+      <c r="AM23" s="4" t="inlineStr"/>
+      <c r="AN23" s="4" t="inlineStr"/>
+      <c r="AO23" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N23" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t>'-0.006</t>
-        </is>
-      </c>
-      <c r="P23" s="3" t="inlineStr"/>
-      <c r="Q23" s="3" t="inlineStr"/>
-      <c r="R23" s="3" t="inlineStr"/>
-      <c r="S23" s="3" t="inlineStr"/>
-      <c r="T23" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U23" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQOHkxSGVRQzdhLUtGMl9CQWlLM05OVklfYk5hXzczZ0I2ajVfUl9RcDhkX19MLWhfWTVENHJmR19yXzZaNXVmZDQ5UGRUVldxNnVHTUpYM1BpUVNScXhzNmJxaENzNm96WkFqOXNpZkFYSjB2bFJ2eDdtM1lMSFBHWW96MU9zRDhmZm5XNEpGR1NWRHJJUk1DdF9nVzNBVVBIOW5fWU1lV2F6dzhUdTZxaE1XbWstZXBKZ3BFVkJoWkJGMUNQRkE?oc=5</t>
-        </is>
-      </c>
-      <c r="V23" s="3" t="inlineStr">
-        <is>
-          <t>CBS Sports</t>
-        </is>
-      </c>
-      <c r="W23" s="3" t="inlineStr">
-        <is>
-          <t>2026 年聖裘德錦標賽電視節目表、報導：在哪裡觀看聯邦快遞杯季後賽第一回合</t>
-        </is>
-      </c>
-      <c r="X23" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y23" s="3" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z23" s="3" t="inlineStr">
-        <is>
-          <t>layoff；layoffs</t>
-        </is>
-      </c>
-      <c r="AA23" s="3" t="inlineStr"/>
-      <c r="AB23" s="3" t="inlineStr"/>
-      <c r="AC23" s="3" t="inlineStr">
-        <is>
-          <t>45e067ff7b8f7136b37e5f84</t>
-        </is>
-      </c>
-      <c r="AD23" s="3" t="inlineStr">
-        <is>
-          <t>c71ad688d3fa04a21868e114</t>
-        </is>
-      </c>
-      <c r="AE23" s="3" t="inlineStr"/>
-      <c r="AF23" s="3" t="inlineStr"/>
-      <c r="AG23" s="3" t="inlineStr"/>
-      <c r="AH23" s="3" t="inlineStr"/>
-      <c r="AI23" s="3" t="inlineStr"/>
-      <c r="AJ23" s="3" t="inlineStr"/>
-      <c r="AK23" s="3" t="inlineStr"/>
-      <c r="AL23" s="3" t="inlineStr"/>
-      <c r="AM23" s="3" t="inlineStr"/>
-      <c r="AN23" s="3" t="inlineStr"/>
-      <c r="AO23" s="3" t="inlineStr"/>
-      <c r="AP23" s="3" t="inlineStr"/>
-      <c r="AQ23" s="3" t="inlineStr"/>
-      <c r="AR23" s="3" t="inlineStr"/>
-      <c r="AS23" s="3" t="inlineStr"/>
-      <c r="AT23" s="3" t="inlineStr"/>
-      <c r="AU23" s="3" t="inlineStr"/>
-      <c r="AV23" s="3" t="inlineStr"/>
-      <c r="AW23" s="3" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX23" s="3" t="inlineStr"/>
-      <c r="AY23" s="3" t="inlineStr"/>
-      <c r="AZ23" s="3" t="inlineStr"/>
-      <c r="BA23" s="3" t="inlineStr"/>
-      <c r="BB23" s="3" t="inlineStr">
-        <is>
-          <t>FDX</t>
-        </is>
-      </c>
-      <c r="BC23" s="3" t="inlineStr">
+      <c r="AP23" s="4" t="inlineStr"/>
+      <c r="AQ23" s="4" t="inlineStr"/>
+      <c r="AR23" s="4" t="inlineStr"/>
+      <c r="AS23" s="4" t="inlineStr"/>
+      <c r="AT23" s="4" t="inlineStr"/>
+      <c r="AU23" s="4" t="inlineStr"/>
+      <c r="AV23" s="4" t="inlineStr"/>
+      <c r="AW23" s="4" t="inlineStr"/>
+      <c r="AX23" s="4" t="inlineStr"/>
+      <c r="AY23" s="4" t="inlineStr"/>
+      <c r="AZ23" s="4" t="inlineStr"/>
+      <c r="BA23" s="4" t="inlineStr"/>
+      <c r="BB23" s="4" t="inlineStr">
+        <is>
+          <t>PNR</t>
+        </is>
+      </c>
+      <c r="BC23" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD23" s="3" t="inlineStr"/>
-      <c r="BE23" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF23" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG23" s="3" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH23" s="3" t="inlineStr"/>
+      <c r="BD23" s="4" t="inlineStr"/>
+      <c r="BE23" s="4" t="inlineStr">
+        <is>
+          <t>公司清單</t>
+        </is>
+      </c>
+      <c r="BF23" s="4" t="inlineStr"/>
+      <c r="BG23" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／交易所參照</t>
+        </is>
+      </c>
+      <c r="BH23" s="4" t="inlineStr"/>
+      <c r="BI23" s="4" t="inlineStr"/>
+      <c r="BJ23" s="4" t="inlineStr"/>
+      <c r="BK23" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL23" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr"/>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>General Motors</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-17T03:38:53+08:00</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>Aces Vs Liberty Gm 2 | 2024 WNBA Playoffs | WNBA Best Bets &amp; Predictions | ChrisBeCappinn Show Golshifteh Farahani (nfYEvsTvq9)</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr"/>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>REGN</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Regeneron Pharmaceuticals, Inc.</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-17T00:00:00+08:00</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>Bronstein, Gewirtz &amp; Grossman LLC Urges Regeneron Pharmaceuticals, Inc. Investors to Act: Class Action Filed Alleging Investor Harm</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr"/>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>重大訴訟</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M24" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N24" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O24" s="4" t="inlineStr">
+        <is>
+          <t>'-0.611</t>
+        </is>
+      </c>
+      <c r="P24" s="4" t="inlineStr"/>
+      <c r="Q24" s="4" t="inlineStr"/>
+      <c r="R24" s="4" t="inlineStr"/>
+      <c r="S24" s="4" t="inlineStr"/>
+      <c r="T24" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U24" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuwJBVV95cUxNQlFEaVkySW9lWldHTWR0aXdTaVlOeC0xRFpMVjRSUWxlbHNUWXhULUFUTFVEcTVkQnpsN1pSTW4xSjB6ZlNJZGczTlQzcnhWbjBhMXRiZEFaZXIyMkg1M2dISFBfM1NJTC1mQzA0dVFKRmk2ektJR1VnZGczdlFMbG1BYkt2WUZlNXBSdm8xUFM1WlBGdzM3NHoxZV9XZGItNmthdkJoc2xoa19PMmRXSV9LOUZ1dE1mVzhXVHdIOG8zMlowNm81dGc2SjF3cTlHUnlpRE9kdFNPLTgyTzdRZ0QzT2pWc2lSSDRldTJKZEpObWZuMm04U0Uxb3R5bXgxQTM5cUN1M3lJZ3g5SFdKMFI5bEY1dEg3SWgzNmVXV1BSUjhBczZrSWk4Ul9oMGhFbEJGWFZpSFZ2Ymc?oc=5</t>
+        </is>
+      </c>
+      <c r="V24" s="4" t="inlineStr">
+        <is>
+          <t>mykxlg.com</t>
+        </is>
+      </c>
+      <c r="W24" s="4" t="inlineStr">
+        <is>
+          <t>Bronstein, Gewirtz &amp; Grossman LLC 敦促 Regeneron Pharmaceuticals, Inc. 投資者採取行動：提起集體訴訟，指控投資者受到傷害</t>
+        </is>
+      </c>
+      <c r="X24" s="4" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y24" s="4" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z24" s="4" t="inlineStr">
+        <is>
+          <t>class action</t>
+        </is>
+      </c>
+      <c r="AA24" s="4" t="inlineStr"/>
+      <c r="AB24" s="4" t="inlineStr">
+        <is>
+          <t>e313433dc1f8469b955af6cc5a1e31b9</t>
+        </is>
+      </c>
+      <c r="AC24" s="4" t="inlineStr">
+        <is>
+          <t>fe41888492b6b722215454c3</t>
+        </is>
+      </c>
+      <c r="AD24" s="4" t="inlineStr">
+        <is>
+          <t>9a0a0fd909ef90019dc43539</t>
+        </is>
+      </c>
+      <c r="AE24" s="4" t="inlineStr"/>
+      <c r="AF24" s="4" t="inlineStr"/>
+      <c r="AG24" s="4" t="inlineStr"/>
+      <c r="AH24" s="4" t="inlineStr"/>
+      <c r="AI24" s="4" t="inlineStr"/>
+      <c r="AJ24" s="4" t="inlineStr"/>
+      <c r="AK24" s="4" t="inlineStr"/>
+      <c r="AL24" s="4" t="inlineStr"/>
+      <c r="AM24" s="4" t="inlineStr"/>
+      <c r="AN24" s="4" t="inlineStr"/>
+      <c r="AO24" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N24" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t>0.014</t>
-        </is>
-      </c>
-      <c r="P24" s="3" t="inlineStr"/>
-      <c r="Q24" s="3" t="inlineStr"/>
-      <c r="R24" s="3" t="inlineStr"/>
-      <c r="S24" s="3" t="inlineStr"/>
-      <c r="T24" s="3" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U24" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTFBZLWVvZmg5YXhKZW5OM3hSZU1sNjBRd0RSRXJpRHRwTmZyV2RYelJucG9CMGlFQVhvUWNKdDBxOGNoWFJTWng0NFNZTHdicHYtY3JhVlpSZjBxZWxwR2xMSw?oc=5</t>
-        </is>
-      </c>
-      <c r="V24" s="3" t="inlineStr">
-        <is>
-          <t>Mshale</t>
-        </is>
-      </c>
-      <c r="W24" s="3" t="inlineStr">
-        <is>
-          <t>王牌 vs 自由 Gm 2 | 2024 年 WNBA 季後賽 | WNBA 最佳投注和預測 | ChrisBeCappinn 秀 Golshifteh Farahani (nfYEvsTvq9)</t>
-        </is>
-      </c>
-      <c r="X24" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y24" s="3" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z24" s="3" t="inlineStr">
-        <is>
-          <t>layoff；layoffs</t>
-        </is>
-      </c>
-      <c r="AA24" s="3" t="inlineStr"/>
-      <c r="AB24" s="3" t="inlineStr"/>
-      <c r="AC24" s="3" t="inlineStr">
-        <is>
-          <t>682c207a9e66b0162d0f8448</t>
-        </is>
-      </c>
-      <c r="AD24" s="3" t="inlineStr">
-        <is>
-          <t>f9f51d4e201987502efdbeb4</t>
-        </is>
-      </c>
-      <c r="AE24" s="3" t="inlineStr"/>
-      <c r="AF24" s="3" t="inlineStr"/>
-      <c r="AG24" s="3" t="inlineStr"/>
-      <c r="AH24" s="3" t="inlineStr"/>
-      <c r="AI24" s="3" t="inlineStr"/>
-      <c r="AJ24" s="3" t="inlineStr"/>
-      <c r="AK24" s="3" t="inlineStr"/>
-      <c r="AL24" s="3" t="inlineStr"/>
-      <c r="AM24" s="3" t="inlineStr"/>
-      <c r="AN24" s="3" t="inlineStr"/>
-      <c r="AO24" s="3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP24" s="3" t="inlineStr"/>
-      <c r="AQ24" s="3" t="inlineStr"/>
-      <c r="AR24" s="3" t="inlineStr"/>
-      <c r="AS24" s="3" t="inlineStr"/>
-      <c r="AT24" s="3" t="inlineStr"/>
-      <c r="AU24" s="3" t="inlineStr"/>
-      <c r="AV24" s="3" t="inlineStr"/>
-      <c r="AW24" s="3" t="inlineStr"/>
-      <c r="AX24" s="3" t="inlineStr"/>
-      <c r="AY24" s="3" t="inlineStr"/>
-      <c r="AZ24" s="3" t="inlineStr"/>
-      <c r="BA24" s="3" t="inlineStr"/>
-      <c r="BB24" s="3" t="inlineStr">
-        <is>
-          <t>GM</t>
-        </is>
-      </c>
-      <c r="BC24" s="3" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD24" s="3" t="inlineStr">
-        <is>
-          <t>GM</t>
-        </is>
-      </c>
-      <c r="BE24" s="3" t="inlineStr"/>
-      <c r="BF24" s="3" t="inlineStr"/>
-      <c r="BG24" s="3" t="inlineStr"/>
-      <c r="BH24" s="3" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>PODD</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>Insulet Corporation</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-17T02:31:00+08:00</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>PODD UPCOMING DEADLINE: Faruqi &amp; Faruqi, LLP Reminds Insulet (PODD) Investors of Securities Class Action Lawsuit Deadline on August 31, 2026</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr"/>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I25" s="4" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K25" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L25" s="4" t="inlineStr"/>
-      <c r="M25" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N25" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O25" s="4" t="inlineStr">
-        <is>
-          <t>'-0.065</t>
-        </is>
-      </c>
-      <c r="P25" s="4" t="inlineStr"/>
-      <c r="Q25" s="4" t="inlineStr"/>
-      <c r="R25" s="4" t="inlineStr"/>
-      <c r="S25" s="4" t="inlineStr"/>
-      <c r="T25" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U25" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxNZlJ3S0xCR2RwRHY1djNQNnYyX29Vd1YwUXhoNGkzWG1vRkxtck9Oamx3WEFCQUZiQVJWbnZBNFJYTm9fRklCVUpnQTVFb1ZQVVI2QW5sdnVlUmJ2NkdIZHRNc242alowMjFMdDA5ejd6eVZpRDB6X3NBTnpISU1FSUZkWlgyVmc1Y1JZbFFwckFwLTVQbmVTZHpocjZuWkpKaV84elp6R2ZCRXZtcjAxcjMzaVNhREpubldSV0FEVVFCQTJnQWl3N3RiejU5Rlc5bTF4OGdCSTFvaUpSQkRNQW1tam8tX2ZWVURiNkViYVBfUGhMM05oU2RfamdHTjRqSllzUnBPak8?oc=5</t>
-        </is>
-      </c>
-      <c r="V25" s="4" t="inlineStr">
-        <is>
-          <t>TMX Newsfile</t>
-        </is>
-      </c>
-      <c r="W25" s="4" t="inlineStr">
-        <is>
-          <t>PODD 截止日期即將到來：Faruqi &amp; Faruqi, LLP 提醒 Insulet (PODD) 投資者證券集體訴訟截止日期為 2026 年 8 月 31 日</t>
-        </is>
-      </c>
-      <c r="X25" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y25" s="4" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z25" s="4" t="inlineStr">
-        <is>
-          <t>class action</t>
-        </is>
-      </c>
-      <c r="AA25" s="4" t="inlineStr"/>
-      <c r="AB25" s="4" t="inlineStr"/>
-      <c r="AC25" s="4" t="inlineStr">
-        <is>
-          <t>512a755fb4b14ed650b4bb48</t>
-        </is>
-      </c>
-      <c r="AD25" s="4" t="inlineStr">
-        <is>
-          <t>b87674e722f99233c85565cf</t>
-        </is>
-      </c>
-      <c r="AE25" s="4" t="inlineStr"/>
-      <c r="AF25" s="4" t="inlineStr"/>
-      <c r="AG25" s="4" t="inlineStr"/>
-      <c r="AH25" s="4" t="inlineStr"/>
-      <c r="AI25" s="4" t="inlineStr"/>
-      <c r="AJ25" s="4" t="inlineStr"/>
-      <c r="AK25" s="4" t="inlineStr"/>
-      <c r="AL25" s="4" t="inlineStr"/>
-      <c r="AM25" s="4" t="inlineStr"/>
-      <c r="AN25" s="4" t="inlineStr"/>
-      <c r="AO25" s="4" t="inlineStr"/>
-      <c r="AP25" s="4" t="inlineStr"/>
-      <c r="AQ25" s="4" t="inlineStr"/>
-      <c r="AR25" s="4" t="inlineStr"/>
-      <c r="AS25" s="4" t="inlineStr"/>
-      <c r="AT25" s="4" t="inlineStr"/>
-      <c r="AU25" s="4" t="inlineStr"/>
-      <c r="AV25" s="4" t="inlineStr"/>
-      <c r="AW25" s="4" t="inlineStr">
+      <c r="AP24" s="4" t="inlineStr"/>
+      <c r="AQ24" s="4" t="inlineStr"/>
+      <c r="AR24" s="4" t="inlineStr"/>
+      <c r="AS24" s="4" t="inlineStr"/>
+      <c r="AT24" s="4" t="inlineStr"/>
+      <c r="AU24" s="4" t="inlineStr"/>
+      <c r="AV24" s="4" t="inlineStr"/>
+      <c r="AW24" s="4" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX25" s="4" t="inlineStr"/>
-      <c r="AY25" s="4" t="inlineStr"/>
-      <c r="AZ25" s="4" t="inlineStr"/>
-      <c r="BA25" s="4" t="inlineStr"/>
-      <c r="BB25" s="4" t="inlineStr">
-        <is>
-          <t>PODD</t>
-        </is>
-      </c>
-      <c r="BC25" s="4" t="inlineStr">
+      <c r="AX24" s="4" t="inlineStr"/>
+      <c r="AY24" s="4" t="inlineStr"/>
+      <c r="AZ24" s="4" t="inlineStr"/>
+      <c r="BA24" s="4" t="inlineStr"/>
+      <c r="BB24" s="4" t="inlineStr">
+        <is>
+          <t>REGN</t>
+        </is>
+      </c>
+      <c r="BC24" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD25" s="4" t="inlineStr"/>
-      <c r="BE25" s="4" t="inlineStr">
+      <c r="BD24" s="4" t="inlineStr"/>
+      <c r="BE24" s="4" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF25" s="4" t="inlineStr">
+      <c r="BF24" s="4" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG25" s="4" t="inlineStr">
+      <c r="BG24" s="4" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH25" s="4" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr"/>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>Costco</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-17T02:15:18+08:00</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>The mistake that helped cost Rebel Creamery $23.8 million and pushed it into bankruptcy</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr"/>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I26" s="5" t="inlineStr">
-        <is>
-          <t>破產</t>
-        </is>
-      </c>
-      <c r="J26" s="5" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K26" s="5" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L26" s="5" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M26" s="5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N26" s="5" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O26" s="5" t="inlineStr">
-        <is>
-          <t>'-0.919</t>
-        </is>
-      </c>
-      <c r="P26" s="5" t="inlineStr"/>
-      <c r="Q26" s="5" t="inlineStr"/>
-      <c r="R26" s="5" t="inlineStr"/>
-      <c r="S26" s="5" t="inlineStr"/>
-      <c r="T26" s="5" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U26" s="5" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPWHJRcURURXlZbXZUVGUwczZYWnBoSGs1SGZEdFRHVEw5NTU0alRoTElPQkd6bnMwMkUzUzQ5emVFMlhYMlNTaWhzUVBfM3pFV1lWV1otV0lLQ2E1ZnZMWG1yYVZSVlJzTGRHdmpIQ3ZiSWF2dDRTYVRhZHdCRXVQcWdrNGt2UnlLbDBTWjY5dWtyMXBLaU95YVp0RUdUQzlibVdjNktLNmZIaUxpSVg2LWFlV1VKUjJPQXlQV1VpcU10R2Y2ZzlpUWtaWW9lcTJ5ZGZDWQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V26" s="5" t="inlineStr">
-        <is>
-          <t>Yahoo</t>
-        </is>
-      </c>
-      <c r="W26" s="5" t="inlineStr">
-        <is>
-          <t>這一錯誤導致 Rebel Creamery 損失 2,380 萬美元，並導致其破產</t>
-        </is>
-      </c>
-      <c r="X26" s="5" t="inlineStr">
-        <is>
-          <t>FINANCIAL</t>
-        </is>
-      </c>
-      <c r="Y26" s="5" t="inlineStr">
-        <is>
-          <t>BANKRUPTCY</t>
-        </is>
-      </c>
-      <c r="Z26" s="5" t="inlineStr">
-        <is>
-          <t>bankruptcy</t>
-        </is>
-      </c>
-      <c r="AA26" s="5" t="inlineStr"/>
-      <c r="AB26" s="5" t="inlineStr"/>
-      <c r="AC26" s="5" t="inlineStr">
-        <is>
-          <t>64a7f574d8b47e024826c657</t>
-        </is>
-      </c>
-      <c r="AD26" s="5" t="inlineStr">
-        <is>
-          <t>4b684ac9d5af90e4b5ffdda5</t>
-        </is>
-      </c>
-      <c r="AE26" s="5" t="inlineStr"/>
-      <c r="AF26" s="5" t="inlineStr"/>
-      <c r="AG26" s="5" t="inlineStr"/>
-      <c r="AH26" s="5" t="inlineStr"/>
-      <c r="AI26" s="5" t="inlineStr"/>
-      <c r="AJ26" s="5" t="inlineStr"/>
-      <c r="AK26" s="5" t="inlineStr"/>
-      <c r="AL26" s="5" t="inlineStr"/>
-      <c r="AM26" s="5" t="inlineStr"/>
-      <c r="AN26" s="5" t="inlineStr"/>
-      <c r="AO26" s="5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP26" s="5" t="inlineStr"/>
-      <c r="AQ26" s="5" t="inlineStr"/>
-      <c r="AR26" s="5" t="inlineStr"/>
-      <c r="AS26" s="5" t="inlineStr"/>
-      <c r="AT26" s="5" t="inlineStr"/>
-      <c r="AU26" s="5" t="inlineStr"/>
-      <c r="AV26" s="5" t="inlineStr"/>
-      <c r="AW26" s="5" t="inlineStr"/>
-      <c r="AX26" s="5" t="inlineStr"/>
-      <c r="AY26" s="5" t="inlineStr"/>
-      <c r="AZ26" s="5" t="inlineStr"/>
-      <c r="BA26" s="5" t="inlineStr"/>
-      <c r="BB26" s="5" t="inlineStr">
-        <is>
-          <t>COST</t>
-        </is>
-      </c>
-      <c r="BC26" s="5" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD26" s="5" t="inlineStr">
-        <is>
-          <t>COST</t>
-        </is>
-      </c>
-      <c r="BE26" s="5" t="inlineStr"/>
-      <c r="BF26" s="5" t="inlineStr"/>
-      <c r="BG26" s="5" t="inlineStr"/>
-      <c r="BH26" s="5" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>PNR</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>Pentair</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-17T01:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-16 | PNR STOCKHOLDER ALERT: Bronstein, Gewirtz and Grossman, LLC Announces that Pentair plc Investors with Substantial Losses Have Opportunity to Lead Class Action Lawsuit! | NYSE:PNR | Press Release</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="inlineStr"/>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I27" s="4" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L27" s="4" t="inlineStr"/>
-      <c r="M27" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N27" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O27" s="4" t="inlineStr">
-        <is>
-          <t>'-0.7</t>
-        </is>
-      </c>
-      <c r="P27" s="4" t="inlineStr"/>
-      <c r="Q27" s="4" t="inlineStr"/>
-      <c r="R27" s="4" t="inlineStr"/>
-      <c r="S27" s="4" t="inlineStr"/>
-      <c r="T27" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U27" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxOQ1kybWpYemNLWEFXdm9Fc1hnR0pOWkNqWkluSWJFMWtkRmNKMDJLRUs1dk5OeEdWSGY3LUZFUVU1cms2dkJaODZDVTdXQmlWTkxQcFcxTVJtVURVbk5zMUhWdkJaeEFIcFRNcjRQUzl5dWJnTDdjWXdFdWlmWF9pTkJvNngwVVhxUE8xMnlMMnJPUFdWMkVSMWpZaVlRWXppdnNnSVBIcnFJN1F4eFFvcGpfWGtZQ0ptOGdXY3N0VmJ4dFdWX3hFZTNCcjRaUQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V27" s="4" t="inlineStr">
-        <is>
-          <t>Stockhouse</t>
-        </is>
-      </c>
-      <c r="W27" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-16 | PNR 股東提醒：Bronstein、Gewirtz 和 Grossman, LLC 宣布遭受重大損失的 Pentair plc 投資者有機會提起集體訴訟！ |紐約證券交易所：PNR |新聞稿</t>
-        </is>
-      </c>
-      <c r="X27" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y27" s="4" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z27" s="4" t="inlineStr">
-        <is>
-          <t>class action</t>
-        </is>
-      </c>
-      <c r="AA27" s="4" t="inlineStr"/>
-      <c r="AB27" s="4" t="inlineStr"/>
-      <c r="AC27" s="4" t="inlineStr">
-        <is>
-          <t>a929e326ef866bb2058da1eb</t>
-        </is>
-      </c>
-      <c r="AD27" s="4" t="inlineStr">
-        <is>
-          <t>ee57266d6e4d6dfd4d68c58c</t>
-        </is>
-      </c>
-      <c r="AE27" s="4" t="inlineStr"/>
-      <c r="AF27" s="4" t="inlineStr"/>
-      <c r="AG27" s="4" t="inlineStr"/>
-      <c r="AH27" s="4" t="inlineStr"/>
-      <c r="AI27" s="4" t="inlineStr"/>
-      <c r="AJ27" s="4" t="inlineStr"/>
-      <c r="AK27" s="4" t="inlineStr"/>
-      <c r="AL27" s="4" t="inlineStr"/>
-      <c r="AM27" s="4" t="inlineStr"/>
-      <c r="AN27" s="4" t="inlineStr"/>
-      <c r="AO27" s="4" t="inlineStr"/>
-      <c r="AP27" s="4" t="inlineStr"/>
-      <c r="AQ27" s="4" t="inlineStr"/>
-      <c r="AR27" s="4" t="inlineStr"/>
-      <c r="AS27" s="4" t="inlineStr"/>
-      <c r="AT27" s="4" t="inlineStr"/>
-      <c r="AU27" s="4" t="inlineStr"/>
-      <c r="AV27" s="4" t="inlineStr"/>
-      <c r="AW27" s="4" t="inlineStr"/>
-      <c r="AX27" s="4" t="inlineStr"/>
-      <c r="AY27" s="4" t="inlineStr"/>
-      <c r="AZ27" s="4" t="inlineStr"/>
-      <c r="BA27" s="4" t="inlineStr"/>
-      <c r="BB27" s="4" t="inlineStr">
-        <is>
-          <t>PNR</t>
-        </is>
-      </c>
-      <c r="BC27" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD27" s="4" t="inlineStr"/>
-      <c r="BE27" s="4" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF27" s="4" t="inlineStr"/>
-      <c r="BG27" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH27" s="4" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>REGN</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>Regeneron Pharmaceuticals, Inc.</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-17T00:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>Bronstein, Gewirtz &amp; Grossman LLC Urges Regeneron Pharmaceuticals, Inc. Investors to Act: Class Action Filed Alleging Investor Harm</t>
-        </is>
-      </c>
-      <c r="G28" s="4" t="inlineStr"/>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I28" s="4" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K28" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L28" s="4" t="inlineStr"/>
-      <c r="M28" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N28" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O28" s="4" t="inlineStr">
-        <is>
-          <t>'-0.611</t>
-        </is>
-      </c>
-      <c r="P28" s="4" t="inlineStr"/>
-      <c r="Q28" s="4" t="inlineStr"/>
-      <c r="R28" s="4" t="inlineStr"/>
-      <c r="S28" s="4" t="inlineStr"/>
-      <c r="T28" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U28" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiuwJBVV95cUxNQlFEaVkySW9lWldHTWR0aXdTaVlOeC0xRFpMVjRSUWxlbHNUWXhULUFUTFVEcTVkQnpsN1pSTW4xSjB6ZlNJZGczTlQzcnhWbjBhMXRiZEFaZXIyMkg1M2dISFBfM1NJTC1mQzA0dVFKRmk2ektJR1VnZGczdlFMbG1BYkt2WUZlNXBSdm8xUFM1WlBGdzM3NHoxZV9XZGItNmthdkJoc2xoa19PMmRXSV9LOUZ1dE1mVzhXVHdIOG8zMlowNm81dGc2SjF3cTlHUnlpRE9kdFNPLTgyTzdRZ0QzT2pWc2lSSDRldTJKZEpObWZuMm04U0Uxb3R5bXgxQTM5cUN1M3lJZ3g5SFdKMFI5bEY1dEg3SWgzNmVXV1BSUjhBczZrSWk4Ul9oMGhFbEJGWFZpSFZ2Ymc?oc=5</t>
-        </is>
-      </c>
-      <c r="V28" s="4" t="inlineStr">
-        <is>
-          <t>mykxlg.com</t>
-        </is>
-      </c>
-      <c r="W28" s="4" t="inlineStr">
-        <is>
-          <t>Bronstein, Gewirtz &amp; Grossman LLC 敦促 Regeneron Pharmaceuticals, Inc. 投資者採取行動：提起集體訴訟，指控投資者受到傷害</t>
-        </is>
-      </c>
-      <c r="X28" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y28" s="4" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z28" s="4" t="inlineStr">
-        <is>
-          <t>class action</t>
-        </is>
-      </c>
-      <c r="AA28" s="4" t="inlineStr"/>
-      <c r="AB28" s="4" t="inlineStr"/>
-      <c r="AC28" s="4" t="inlineStr">
-        <is>
-          <t>fe41888492b6b722215454c3</t>
-        </is>
-      </c>
-      <c r="AD28" s="4" t="inlineStr">
-        <is>
-          <t>9a0a0fd909ef90019dc43539</t>
-        </is>
-      </c>
-      <c r="AE28" s="4" t="inlineStr"/>
-      <c r="AF28" s="4" t="inlineStr"/>
-      <c r="AG28" s="4" t="inlineStr"/>
-      <c r="AH28" s="4" t="inlineStr"/>
-      <c r="AI28" s="4" t="inlineStr"/>
-      <c r="AJ28" s="4" t="inlineStr"/>
-      <c r="AK28" s="4" t="inlineStr"/>
-      <c r="AL28" s="4" t="inlineStr"/>
-      <c r="AM28" s="4" t="inlineStr"/>
-      <c r="AN28" s="4" t="inlineStr"/>
-      <c r="AO28" s="4" t="inlineStr"/>
-      <c r="AP28" s="4" t="inlineStr"/>
-      <c r="AQ28" s="4" t="inlineStr"/>
-      <c r="AR28" s="4" t="inlineStr"/>
-      <c r="AS28" s="4" t="inlineStr"/>
-      <c r="AT28" s="4" t="inlineStr"/>
-      <c r="AU28" s="4" t="inlineStr"/>
-      <c r="AV28" s="4" t="inlineStr"/>
-      <c r="AW28" s="4" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="AX28" s="4" t="inlineStr"/>
-      <c r="AY28" s="4" t="inlineStr"/>
-      <c r="AZ28" s="4" t="inlineStr"/>
-      <c r="BA28" s="4" t="inlineStr"/>
-      <c r="BB28" s="4" t="inlineStr">
-        <is>
-          <t>REGN</t>
-        </is>
-      </c>
-      <c r="BC28" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD28" s="4" t="inlineStr"/>
-      <c r="BE28" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF28" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG28" s="4" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH28" s="4" t="inlineStr"/>
+      <c r="BH24" s="4" t="inlineStr"/>
+      <c r="BI24" s="4" t="inlineStr"/>
+      <c r="BJ24" s="4" t="inlineStr"/>
+      <c r="BK24" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL24" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH28"/>
+  <autoFilter ref="A1:BL24"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15099,7 +15087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH22"/>
+  <dimension ref="A1:BL20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -15162,6 +15150,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15463,6 +15455,26 @@
       <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Ticker稽核警示</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
         </is>
       </c>
     </row>
@@ -15639,6 +15651,10 @@
       </c>
       <c r="BG2" s="2" t="inlineStr"/>
       <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr"/>
+      <c r="BL2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -15805,6 +15821,10 @@
       <c r="BF3" s="2" t="inlineStr"/>
       <c r="BG3" s="2" t="inlineStr"/>
       <c r="BH3" s="2" t="inlineStr"/>
+      <c r="BI3" s="2" t="inlineStr"/>
+      <c r="BJ3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr"/>
+      <c r="BL3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -15971,6 +15991,10 @@
       <c r="BF4" s="2" t="inlineStr"/>
       <c r="BG4" s="2" t="inlineStr"/>
       <c r="BH4" s="2" t="inlineStr"/>
+      <c r="BI4" s="2" t="inlineStr"/>
+      <c r="BJ4" s="2" t="inlineStr"/>
+      <c r="BK4" s="2" t="inlineStr"/>
+      <c r="BL4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -16137,6 +16161,10 @@
       <c r="BF5" s="3" t="inlineStr"/>
       <c r="BG5" s="3" t="inlineStr"/>
       <c r="BH5" s="3" t="inlineStr"/>
+      <c r="BI5" s="3" t="inlineStr"/>
+      <c r="BJ5" s="3" t="inlineStr"/>
+      <c r="BK5" s="3" t="inlineStr"/>
+      <c r="BL5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -16311,6 +16339,10 @@
       </c>
       <c r="BG6" s="2" t="inlineStr"/>
       <c r="BH6" s="2" t="inlineStr"/>
+      <c r="BI6" s="2" t="inlineStr"/>
+      <c r="BJ6" s="2" t="inlineStr"/>
+      <c r="BK6" s="2" t="inlineStr"/>
+      <c r="BL6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -16477,6 +16509,10 @@
       <c r="BF7" s="2" t="inlineStr"/>
       <c r="BG7" s="2" t="inlineStr"/>
       <c r="BH7" s="2" t="inlineStr"/>
+      <c r="BI7" s="2" t="inlineStr"/>
+      <c r="BJ7" s="2" t="inlineStr"/>
+      <c r="BK7" s="2" t="inlineStr"/>
+      <c r="BL7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -16643,6 +16679,10 @@
       <c r="BF8" s="2" t="inlineStr"/>
       <c r="BG8" s="2" t="inlineStr"/>
       <c r="BH8" s="2" t="inlineStr"/>
+      <c r="BI8" s="2" t="inlineStr"/>
+      <c r="BJ8" s="2" t="inlineStr"/>
+      <c r="BK8" s="2" t="inlineStr"/>
+      <c r="BL8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -16809,6 +16849,10 @@
       <c r="BF9" s="2" t="inlineStr"/>
       <c r="BG9" s="2" t="inlineStr"/>
       <c r="BH9" s="2" t="inlineStr"/>
+      <c r="BI9" s="2" t="inlineStr"/>
+      <c r="BJ9" s="2" t="inlineStr"/>
+      <c r="BK9" s="2" t="inlineStr"/>
+      <c r="BL9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -16983,6 +17027,10 @@
       </c>
       <c r="BG10" s="3" t="inlineStr"/>
       <c r="BH10" s="3" t="inlineStr"/>
+      <c r="BI10" s="3" t="inlineStr"/>
+      <c r="BJ10" s="3" t="inlineStr"/>
+      <c r="BK10" s="3" t="inlineStr"/>
+      <c r="BL10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -17157,6 +17205,10 @@
       </c>
       <c r="BG11" s="2" t="inlineStr"/>
       <c r="BH11" s="2" t="inlineStr"/>
+      <c r="BI11" s="2" t="inlineStr"/>
+      <c r="BJ11" s="2" t="inlineStr"/>
+      <c r="BK11" s="2" t="inlineStr"/>
+      <c r="BL11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -17323,6 +17375,10 @@
       <c r="BF12" s="2" t="inlineStr"/>
       <c r="BG12" s="2" t="inlineStr"/>
       <c r="BH12" s="2" t="inlineStr"/>
+      <c r="BI12" s="2" t="inlineStr"/>
+      <c r="BJ12" s="2" t="inlineStr"/>
+      <c r="BK12" s="2" t="inlineStr"/>
+      <c r="BL12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -17497,6 +17553,10 @@
       </c>
       <c r="BG13" s="2" t="inlineStr"/>
       <c r="BH13" s="2" t="inlineStr"/>
+      <c r="BI13" s="2" t="inlineStr"/>
+      <c r="BJ13" s="2" t="inlineStr"/>
+      <c r="BK13" s="2" t="inlineStr"/>
+      <c r="BL13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -17663,6 +17723,10 @@
       <c r="BF14" s="3" t="inlineStr"/>
       <c r="BG14" s="3" t="inlineStr"/>
       <c r="BH14" s="3" t="inlineStr"/>
+      <c r="BI14" s="3" t="inlineStr"/>
+      <c r="BJ14" s="3" t="inlineStr"/>
+      <c r="BK14" s="3" t="inlineStr"/>
+      <c r="BL14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -17837,346 +17901,358 @@
       </c>
       <c r="BG15" s="3" t="inlineStr"/>
       <c r="BH15" s="3" t="inlineStr"/>
+      <c r="BI15" s="3" t="inlineStr"/>
+      <c r="BJ15" s="3" t="inlineStr"/>
+      <c r="BK15" s="3" t="inlineStr"/>
+      <c r="BL15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>Intercontinental Exchange</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-17T05:12:05+08:00</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>Popular ice cream brand sold at Walmart and Target files for bankruptcy</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>破產</t>
-        </is>
-      </c>
-      <c r="J16" s="5" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K16" s="5" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr"/>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>General Motors</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-17T03:38:53+08:00</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Aces Vs Liberty Gm 2 | 2024 WNBA Playoffs | WNBA Best Bets &amp; Predictions | ChrisBeCappinn Show Golshifteh Farahani (nfYEvsTvq9)</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>裁員或人力縮減</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L16" s="5" t="inlineStr">
+      <c r="L16" s="3" t="inlineStr">
         <is>
           <t>待人工覆核</t>
         </is>
       </c>
-      <c r="M16" s="5" t="inlineStr">
+      <c r="M16" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N16" s="5" t="inlineStr">
+      <c r="N16" s="3" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O16" s="5" t="inlineStr">
-        <is>
-          <t>'-0.757</t>
-        </is>
-      </c>
-      <c r="P16" s="5" t="inlineStr"/>
-      <c r="Q16" s="5" t="inlineStr"/>
-      <c r="R16" s="5" t="inlineStr"/>
-      <c r="S16" s="5" t="inlineStr"/>
-      <c r="T16" s="5" t="inlineStr">
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>0.014</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr"/>
+      <c r="Q16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="inlineStr"/>
+      <c r="S16" s="3" t="inlineStr"/>
+      <c r="T16" s="3" t="inlineStr">
         <is>
           <t>主體證據不足</t>
         </is>
       </c>
-      <c r="U16" s="5" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQZ2NOcHBBeFgwamJCQ0hNWmJkLXJHOTZjUU5aT1hVOEpfSzY1aW8wZ2NLMFVYNE5QZG5zLUxMTGYzWUQzLTV1SDJXbkRuZnJoWW92R250WmpMaXZEZFFHajBqU2Q2NG44aU1qX2hUOVdyZnhsQlYxeTVrakhOYTZyT3kzaWpNUGRWLWZ4andORUJrMm9nVzk0bQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V16" s="5" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W16" s="5" t="inlineStr">
-        <is>
-          <t>沃爾瑪和塔吉特銷售的熱門冰淇淋品牌申請破產</t>
-        </is>
-      </c>
-      <c r="X16" s="5" t="inlineStr">
-        <is>
-          <t>FINANCIAL</t>
-        </is>
-      </c>
-      <c r="Y16" s="5" t="inlineStr">
-        <is>
-          <t>BANKRUPTCY</t>
-        </is>
-      </c>
-      <c r="Z16" s="5" t="inlineStr">
-        <is>
-          <t>bankruptcy</t>
-        </is>
-      </c>
-      <c r="AA16" s="5" t="inlineStr"/>
-      <c r="AB16" s="5" t="inlineStr"/>
-      <c r="AC16" s="5" t="inlineStr">
-        <is>
-          <t>35a1e5ff35be561beca55240</t>
-        </is>
-      </c>
-      <c r="AD16" s="5" t="inlineStr">
-        <is>
-          <t>11dfdd497cf6d878e41e446f</t>
-        </is>
-      </c>
-      <c r="AE16" s="5" t="inlineStr"/>
-      <c r="AF16" s="5" t="inlineStr"/>
-      <c r="AG16" s="5" t="inlineStr"/>
-      <c r="AH16" s="5" t="inlineStr"/>
-      <c r="AI16" s="5" t="inlineStr"/>
-      <c r="AJ16" s="5" t="inlineStr"/>
-      <c r="AK16" s="5" t="inlineStr"/>
-      <c r="AL16" s="5" t="inlineStr"/>
-      <c r="AM16" s="5" t="inlineStr"/>
-      <c r="AN16" s="5" t="inlineStr"/>
-      <c r="AO16" s="5" t="inlineStr">
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTFBZLWVvZmg5YXhKZW5OM3hSZU1sNjBRd0RSRXJpRHRwTmZyV2RYelJucG9CMGlFQVhvUWNKdDBxOGNoWFJTWng0NFNZTHdicHYtY3JhVlpSZjBxZWxwR2xMSw?oc=5</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t>Mshale</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
+          <t>王牌 vs 自由 Gm 2 | 2024 年 WNBA 季後賽 | WNBA 最佳投注和預測 | ChrisBeCappinn 秀 Golshifteh Farahani (nfYEvsTvq9)</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y16" s="3" t="inlineStr">
+        <is>
+          <t>WORKFORCE_REDUCTION</t>
+        </is>
+      </c>
+      <c r="Z16" s="3" t="inlineStr">
+        <is>
+          <t>layoff；layoffs</t>
+        </is>
+      </c>
+      <c r="AA16" s="3" t="inlineStr"/>
+      <c r="AB16" s="3" t="inlineStr"/>
+      <c r="AC16" s="3" t="inlineStr">
+        <is>
+          <t>682c207a9e66b0162d0f8448</t>
+        </is>
+      </c>
+      <c r="AD16" s="3" t="inlineStr">
+        <is>
+          <t>f9f51d4e201987502efdbeb4</t>
+        </is>
+      </c>
+      <c r="AE16" s="3" t="inlineStr"/>
+      <c r="AF16" s="3" t="inlineStr"/>
+      <c r="AG16" s="3" t="inlineStr"/>
+      <c r="AH16" s="3" t="inlineStr"/>
+      <c r="AI16" s="3" t="inlineStr"/>
+      <c r="AJ16" s="3" t="inlineStr"/>
+      <c r="AK16" s="3" t="inlineStr"/>
+      <c r="AL16" s="3" t="inlineStr"/>
+      <c r="AM16" s="3" t="inlineStr"/>
+      <c r="AN16" s="3" t="inlineStr"/>
+      <c r="AO16" s="3" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AP16" s="5" t="inlineStr"/>
-      <c r="AQ16" s="5" t="inlineStr"/>
-      <c r="AR16" s="5" t="inlineStr"/>
-      <c r="AS16" s="5" t="inlineStr"/>
-      <c r="AT16" s="5" t="inlineStr"/>
-      <c r="AU16" s="5" t="inlineStr"/>
-      <c r="AV16" s="5" t="inlineStr"/>
-      <c r="AW16" s="5" t="inlineStr"/>
-      <c r="AX16" s="5" t="inlineStr"/>
-      <c r="AY16" s="5" t="inlineStr"/>
-      <c r="AZ16" s="5" t="inlineStr"/>
-      <c r="BA16" s="5" t="inlineStr"/>
-      <c r="BB16" s="5" t="inlineStr">
-        <is>
-          <t>ICE</t>
-        </is>
-      </c>
-      <c r="BC16" s="5" t="inlineStr">
+      <c r="AP16" s="3" t="inlineStr"/>
+      <c r="AQ16" s="3" t="inlineStr"/>
+      <c r="AR16" s="3" t="inlineStr"/>
+      <c r="AS16" s="3" t="inlineStr"/>
+      <c r="AT16" s="3" t="inlineStr"/>
+      <c r="AU16" s="3" t="inlineStr"/>
+      <c r="AV16" s="3" t="inlineStr"/>
+      <c r="AW16" s="3" t="inlineStr"/>
+      <c r="AX16" s="3" t="inlineStr"/>
+      <c r="AY16" s="3" t="inlineStr"/>
+      <c r="AZ16" s="3" t="inlineStr"/>
+      <c r="BA16" s="3" t="inlineStr"/>
+      <c r="BB16" s="3" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="BC16" s="3" t="inlineStr">
         <is>
           <t>主體證據不足</t>
         </is>
       </c>
-      <c r="BD16" s="5" t="inlineStr">
-        <is>
-          <t>ICE</t>
-        </is>
-      </c>
-      <c r="BE16" s="5" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF16" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG16" s="5" t="inlineStr"/>
-      <c r="BH16" s="5" t="inlineStr"/>
+      <c r="BD16" s="3" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="BE16" s="3" t="inlineStr"/>
+      <c r="BF16" s="3" t="inlineStr"/>
+      <c r="BG16" s="3" t="inlineStr"/>
+      <c r="BH16" s="3" t="inlineStr"/>
+      <c r="BI16" s="3" t="inlineStr"/>
+      <c r="BJ16" s="3" t="inlineStr"/>
+      <c r="BK16" s="3" t="inlineStr"/>
+      <c r="BL16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr"/>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>General Motors</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-17T03:38:53+08:00</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>Aces Vs Liberty Gm 2 | 2024 WNBA Playoffs | WNBA Best Bets &amp; Predictions | ChrisBeCappinn Show Golshifteh Farahani (nfYEvsTvq9)</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr"/>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr"/>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Deere &amp; Company</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17T03:20:18+08:00</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Abelardo de la Espriella asks Donald Trump to suspend tariffs to help Colombia earthquake recovery</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>關稅</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>僅紀錄</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L17" s="3" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>待人工覆核</t>
         </is>
       </c>
-      <c r="M17" s="3" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N17" s="3" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>0.014</t>
-        </is>
-      </c>
-      <c r="P17" s="3" t="inlineStr"/>
-      <c r="Q17" s="3" t="inlineStr"/>
-      <c r="R17" s="3" t="inlineStr"/>
-      <c r="S17" s="3" t="inlineStr"/>
-      <c r="T17" s="3" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>'-0.808</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr">
         <is>
           <t>主體證據不足</t>
         </is>
       </c>
-      <c r="U17" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTFBZLWVvZmg5YXhKZW5OM3hSZU1sNjBRd0RSRXJpRHRwTmZyV2RYelJucG9CMGlFQVhvUWNKdDBxOGNoWFJTWng0NFNZTHdicHYtY3JhVlpSZjBxZWxwR2xMSw?oc=5</t>
-        </is>
-      </c>
-      <c r="V17" s="3" t="inlineStr">
-        <is>
-          <t>Mshale</t>
-        </is>
-      </c>
-      <c r="W17" s="3" t="inlineStr">
-        <is>
-          <t>王牌 vs 自由 Gm 2 | 2024 年 WNBA 季後賽 | WNBA 最佳投注和預測 | ChrisBeCappinn 秀 Golshifteh Farahani (nfYEvsTvq9)</t>
-        </is>
-      </c>
-      <c r="X17" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y17" s="3" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z17" s="3" t="inlineStr">
-        <is>
-          <t>layoff；layoffs</t>
-        </is>
-      </c>
-      <c r="AA17" s="3" t="inlineStr"/>
-      <c r="AB17" s="3" t="inlineStr"/>
-      <c r="AC17" s="3" t="inlineStr">
-        <is>
-          <t>682c207a9e66b0162d0f8448</t>
-        </is>
-      </c>
-      <c r="AD17" s="3" t="inlineStr">
-        <is>
-          <t>f9f51d4e201987502efdbeb4</t>
-        </is>
-      </c>
-      <c r="AE17" s="3" t="inlineStr"/>
-      <c r="AF17" s="3" t="inlineStr"/>
-      <c r="AG17" s="3" t="inlineStr"/>
-      <c r="AH17" s="3" t="inlineStr"/>
-      <c r="AI17" s="3" t="inlineStr"/>
-      <c r="AJ17" s="3" t="inlineStr"/>
-      <c r="AK17" s="3" t="inlineStr"/>
-      <c r="AL17" s="3" t="inlineStr"/>
-      <c r="AM17" s="3" t="inlineStr"/>
-      <c r="AN17" s="3" t="inlineStr"/>
-      <c r="AO17" s="3" t="inlineStr">
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNVXhoZm85Q3Y5NklZRk8tUUJ6OGc3M2FNOWE0Z1pYWENfdmZVT0FUQ0h4SEJYcWc5THJjRjh3bW1xczhERElnNXpUVko0eEVZLVRLcWkwaTFDX3NBNGl2T1BnYldKVlFoZzltSlMyalVmMEJ2YmRrM19NN0lNQmZBNVp5THl1NERLT1BsMnA5ZXNkTXJUQlpReS1aNE5FXzQ0TVFqUTlsUzNaX0xMM0JsQzVlTkdvNE5OWW9Lb3NNcWJUNG9XSkJvM0xWd9IB0AFBVV95cUxQMU5vNHRDdjVYMEhQQnVvNVRPVTdZVmdBRm1zalNuYmlaSURqckF1NU5PVl9zV0ZSYngweG5KdjFaY25LekVYajFEWDZlQk01V2xTc0FkcGlnSGZWaXpjcV9hNkpzcndHSEZTNGtHTzJzZy0tN0pFYi1XM2t0VTV0ZEdfazFDNElQTjlDeFFGa09MNHRlTU1jcGVZUDZ2al8xMW54UmVNc0E0UFB5ckd5N0Nkb1B1Ynh2a1FxRVQ5YnM5UUJ4Zl9DTU5aanl3U05G?oc=5</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>ABC7 Chicago</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>阿韋拉多·德拉埃斯普里埃拉要求唐納德·特朗普暫停關稅以幫助哥倫比亞地震恢復</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>GEOPOLITICAL</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>TARIFF</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>tariff</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr"/>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>60f9311faf81322706bf721c</t>
+        </is>
+      </c>
+      <c r="AD17" s="2" t="inlineStr">
+        <is>
+          <t>267246deed9567d1b709317e</t>
+        </is>
+      </c>
+      <c r="AE17" s="2" t="inlineStr"/>
+      <c r="AF17" s="2" t="inlineStr"/>
+      <c r="AG17" s="2" t="inlineStr"/>
+      <c r="AH17" s="2" t="inlineStr"/>
+      <c r="AI17" s="2" t="inlineStr"/>
+      <c r="AJ17" s="2" t="inlineStr"/>
+      <c r="AK17" s="2" t="inlineStr"/>
+      <c r="AL17" s="2" t="inlineStr"/>
+      <c r="AM17" s="2" t="inlineStr"/>
+      <c r="AN17" s="2" t="inlineStr"/>
+      <c r="AO17" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AP17" s="3" t="inlineStr"/>
-      <c r="AQ17" s="3" t="inlineStr"/>
-      <c r="AR17" s="3" t="inlineStr"/>
-      <c r="AS17" s="3" t="inlineStr"/>
-      <c r="AT17" s="3" t="inlineStr"/>
-      <c r="AU17" s="3" t="inlineStr"/>
-      <c r="AV17" s="3" t="inlineStr"/>
-      <c r="AW17" s="3" t="inlineStr"/>
-      <c r="AX17" s="3" t="inlineStr"/>
-      <c r="AY17" s="3" t="inlineStr"/>
-      <c r="AZ17" s="3" t="inlineStr"/>
-      <c r="BA17" s="3" t="inlineStr"/>
-      <c r="BB17" s="3" t="inlineStr">
-        <is>
-          <t>GM</t>
-        </is>
-      </c>
-      <c r="BC17" s="3" t="inlineStr">
+      <c r="AP17" s="2" t="inlineStr"/>
+      <c r="AQ17" s="2" t="inlineStr"/>
+      <c r="AR17" s="2" t="inlineStr"/>
+      <c r="AS17" s="2" t="inlineStr"/>
+      <c r="AT17" s="2" t="inlineStr"/>
+      <c r="AU17" s="2" t="inlineStr"/>
+      <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" s="2" t="inlineStr"/>
+      <c r="AX17" s="2" t="inlineStr"/>
+      <c r="AY17" s="2" t="inlineStr"/>
+      <c r="AZ17" s="2" t="inlineStr"/>
+      <c r="BA17" s="2" t="inlineStr"/>
+      <c r="BB17" s="2" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="BC17" s="2" t="inlineStr">
         <is>
           <t>主體證據不足</t>
         </is>
       </c>
-      <c r="BD17" s="3" t="inlineStr">
-        <is>
-          <t>GM</t>
-        </is>
-      </c>
-      <c r="BE17" s="3" t="inlineStr"/>
-      <c r="BF17" s="3" t="inlineStr"/>
-      <c r="BG17" s="3" t="inlineStr"/>
-      <c r="BH17" s="3" t="inlineStr"/>
+      <c r="BD17" s="2" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="BE17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF17" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
+      <c r="BG17" s="2" t="inlineStr"/>
+      <c r="BH17" s="2" t="inlineStr"/>
+      <c r="BI17" s="2" t="inlineStr"/>
+      <c r="BJ17" s="2" t="inlineStr"/>
+      <c r="BK17" s="2" t="inlineStr"/>
+      <c r="BL17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -18192,28 +18268,28 @@
       <c r="C18" s="2" t="inlineStr"/>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Deere &amp; Company</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17T03:20:18+08:00</t>
+          <t>2026-08-17T01:44:00+08:00</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Abelardo de la Espriella asks Donald Trump to suspend tariffs to help Colombia earthquake recovery</t>
+          <t>'Mother Nature always wins' | Flood waters cut through Hazel Dell Parkway bridge, crews asking for space as they work to assess damage</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>關稅</t>
+          <t>天災</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -18243,7 +18319,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>'-0.808</t>
+          <t>'-0.791</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr"/>
@@ -18257,44 +18333,44 @@
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNVXhoZm85Q3Y5NklZRk8tUUJ6OGc3M2FNOWE0Z1pYWENfdmZVT0FUQ0h4SEJYcWc5THJjRjh3bW1xczhERElnNXpUVko0eEVZLVRLcWkwaTFDX3NBNGl2T1BnYldKVlFoZzltSlMyalVmMEJ2YmRrM19NN0lNQmZBNVp5THl1NERLT1BsMnA5ZXNkTXJUQlpReS1aNE5FXzQ0TVFqUTlsUzNaX0xMM0JsQzVlTkdvNE5OWW9Lb3NNcWJUNG9XSkJvM0xWd9IB0AFBVV95cUxQMU5vNHRDdjVYMEhQQnVvNVRPVTdZVmdBRm1zalNuYmlaSURqckF1NU5PVl9zV0ZSYngweG5KdjFaY25LekVYajFEWDZlQk01V2xTc0FkcGlnSGZWaXpjcV9hNkpzcndHSEZTNGtHTzJzZy0tN0pFYi1XM2t0VTV0ZEdfazFDNElQTjlDeFFGa09MNHRlTU1jcGVZUDZ2al8xMW54UmVNc0E0UFB5ckd5N0Nkb1B1Ynh2a1FxRVQ5YnM5UUJ4Zl9DTU5aanl3U05G?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAJBVV95cUxOU2dmNWppUU1Sbm1ZM3JSWGNUSy1McFNORVExYWJ5LVFfZ3dlZHZjQ015VHpBWGtoSFQ2RmQyb1VkQ2NMS3lMZEpaUEZ4UDRqLVVOajB5UEM1aVU5cks0Z2s5dk4xWDZmWnhwTDVKN1hQbEZKLWxneDUwVjRPR0w2dXh6RmM3YlphYWhuTlFKcmRBNnF4aHYzS2pHa00xS1QwbVcwaDVyLThGQ3ZnbUlPMFRUS1JLSmloc0U4OFV4SVZfNDZvelJnOXpmTENwWE8xSjc2VUt3NFpjb29aR3VmaG9uT2hzUWRrTTNGeWUxaUYybTA0dzdUcXJ6ZngyQy1SU0Fpb2U5dkVFdHROYWlrRFVvRWpJeTF5d25YUDZNejBZY1lkc2lXdjBrcVF2OUstbUhhTlB6YjdSX05paXdpMmE4Mlk?oc=5</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>ABC7 Chicago</t>
+          <t>WTHR</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>阿韋拉多·德拉埃斯普里埃拉要求唐納德·特朗普暫停關稅以幫助哥倫比亞地震恢復</t>
+          <t>「大自然總是勝利」|洪水沖垮了 Hazel Dell Parkway 大橋，工作人員在評估損失時要求騰出空間</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>GEOPOLITICAL</t>
+          <t>OPERATIONS</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>TARIFF</t>
+          <t>NATURAL_DISASTER</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>tariff</t>
+          <t>flood</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr"/>
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>60f9311faf81322706bf721c</t>
+          <t>ca87d494360b0f73a396d9be</t>
         </is>
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>267246deed9567d1b709317e</t>
+          <t>de88dbbab1bc44a277cf9d86</t>
         </is>
       </c>
       <c r="AE18" s="2" t="inlineStr"/>
@@ -18326,7 +18402,7 @@
       <c r="BA18" s="2" t="inlineStr"/>
       <c r="BB18" s="2" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="BC18" s="2" t="inlineStr">
@@ -18336,7 +18412,7 @@
       </c>
       <c r="BD18" s="2" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="BE18" s="2" t="inlineStr">
@@ -18351,172 +18427,180 @@
       </c>
       <c r="BG18" s="2" t="inlineStr"/>
       <c r="BH18" s="2" t="inlineStr"/>
+      <c r="BI18" s="2" t="inlineStr"/>
+      <c r="BJ18" s="2" t="inlineStr"/>
+      <c r="BK18" s="2" t="inlineStr"/>
+      <c r="BL18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr"/>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>Costco</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-17T02:15:18+08:00</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>The mistake that helped cost Rebel Creamery $23.8 million and pushed it into bankruptcy</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr"/>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I19" s="5" t="inlineStr">
-        <is>
-          <t>破產</t>
-        </is>
-      </c>
-      <c r="J19" s="5" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K19" s="5" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr"/>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Estée Lauder Companies (The)</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17T01:39:25+08:00</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Montana in Far East El Paso reopened after flooding caused overnight closure</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>天災</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>僅紀錄</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L19" s="5" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>待人工覆核</t>
         </is>
       </c>
-      <c r="M19" s="5" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N19" s="5" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O19" s="5" t="inlineStr">
-        <is>
-          <t>'-0.919</t>
-        </is>
-      </c>
-      <c r="P19" s="5" t="inlineStr"/>
-      <c r="Q19" s="5" t="inlineStr"/>
-      <c r="R19" s="5" t="inlineStr"/>
-      <c r="S19" s="5" t="inlineStr"/>
-      <c r="T19" s="5" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>'-0.699</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr"/>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr">
         <is>
           <t>主體證據不足</t>
         </is>
       </c>
-      <c r="U19" s="5" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPWHJRcURURXlZbXZUVGUwczZYWnBoSGs1SGZEdFRHVEw5NTU0alRoTElPQkd6bnMwMkUzUzQ5emVFMlhYMlNTaWhzUVBfM3pFV1lWV1otV0lLQ2E1ZnZMWG1yYVZSVlJzTGRHdmpIQ3ZiSWF2dDRTYVRhZHdCRXVQcWdrNGt2UnlLbDBTWjY5dWtyMXBLaU95YVp0RUdUQzlibVdjNktLNmZIaUxpSVg2LWFlV1VKUjJPQXlQV1VpcU10R2Y2ZzlpUWtaWW9lcTJ5ZGZDWQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V19" s="5" t="inlineStr">
-        <is>
-          <t>Yahoo</t>
-        </is>
-      </c>
-      <c r="W19" s="5" t="inlineStr">
-        <is>
-          <t>這一錯誤導致 Rebel Creamery 損失 2,380 萬美元，並導致其破產</t>
-        </is>
-      </c>
-      <c r="X19" s="5" t="inlineStr">
-        <is>
-          <t>FINANCIAL</t>
-        </is>
-      </c>
-      <c r="Y19" s="5" t="inlineStr">
-        <is>
-          <t>BANKRUPTCY</t>
-        </is>
-      </c>
-      <c r="Z19" s="5" t="inlineStr">
-        <is>
-          <t>bankruptcy</t>
-        </is>
-      </c>
-      <c r="AA19" s="5" t="inlineStr"/>
-      <c r="AB19" s="5" t="inlineStr"/>
-      <c r="AC19" s="5" t="inlineStr">
-        <is>
-          <t>64a7f574d8b47e024826c657</t>
-        </is>
-      </c>
-      <c r="AD19" s="5" t="inlineStr">
-        <is>
-          <t>4b684ac9d5af90e4b5ffdda5</t>
-        </is>
-      </c>
-      <c r="AE19" s="5" t="inlineStr"/>
-      <c r="AF19" s="5" t="inlineStr"/>
-      <c r="AG19" s="5" t="inlineStr"/>
-      <c r="AH19" s="5" t="inlineStr"/>
-      <c r="AI19" s="5" t="inlineStr"/>
-      <c r="AJ19" s="5" t="inlineStr"/>
-      <c r="AK19" s="5" t="inlineStr"/>
-      <c r="AL19" s="5" t="inlineStr"/>
-      <c r="AM19" s="5" t="inlineStr"/>
-      <c r="AN19" s="5" t="inlineStr"/>
-      <c r="AO19" s="5" t="inlineStr">
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxONGVFZEI4OF9jSVdIU0NVU08xRnFuaUtBMXR3NkNBOHlRUEFsc2szb1VfODhDeXB4N2pQTFctUnZzV2xsUHBfc05BenVYYkFhRGI4RGozdjZWbV9VX0prTTJpTEh3RWF4WHBoTnJfb281M0d2V1k4UF9VbERjcnNBNzV0VDVKOWxaQUJFUG5Ock9OVER2cmMzR2tnbFRkQkVkaGdxN0Z2S2JKMzBiOTZR?oc=5</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>KVIA</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>蒙大拿州遠東地區埃爾帕索在洪水導致夜間關閉後重新開放</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>NATURAL_DISASTER</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>flood；flooding</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr"/>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>8baabf861da98886f444cefa</t>
+        </is>
+      </c>
+      <c r="AD19" s="2" t="inlineStr">
+        <is>
+          <t>242e7a8d72bcf93bd705396c</t>
+        </is>
+      </c>
+      <c r="AE19" s="2" t="inlineStr"/>
+      <c r="AF19" s="2" t="inlineStr"/>
+      <c r="AG19" s="2" t="inlineStr"/>
+      <c r="AH19" s="2" t="inlineStr"/>
+      <c r="AI19" s="2" t="inlineStr"/>
+      <c r="AJ19" s="2" t="inlineStr"/>
+      <c r="AK19" s="2" t="inlineStr"/>
+      <c r="AL19" s="2" t="inlineStr"/>
+      <c r="AM19" s="2" t="inlineStr"/>
+      <c r="AN19" s="2" t="inlineStr"/>
+      <c r="AO19" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AP19" s="5" t="inlineStr"/>
-      <c r="AQ19" s="5" t="inlineStr"/>
-      <c r="AR19" s="5" t="inlineStr"/>
-      <c r="AS19" s="5" t="inlineStr"/>
-      <c r="AT19" s="5" t="inlineStr"/>
-      <c r="AU19" s="5" t="inlineStr"/>
-      <c r="AV19" s="5" t="inlineStr"/>
-      <c r="AW19" s="5" t="inlineStr"/>
-      <c r="AX19" s="5" t="inlineStr"/>
-      <c r="AY19" s="5" t="inlineStr"/>
-      <c r="AZ19" s="5" t="inlineStr"/>
-      <c r="BA19" s="5" t="inlineStr"/>
-      <c r="BB19" s="5" t="inlineStr">
-        <is>
-          <t>COST</t>
-        </is>
-      </c>
-      <c r="BC19" s="5" t="inlineStr">
+      <c r="AP19" s="2" t="inlineStr"/>
+      <c r="AQ19" s="2" t="inlineStr"/>
+      <c r="AR19" s="2" t="inlineStr"/>
+      <c r="AS19" s="2" t="inlineStr"/>
+      <c r="AT19" s="2" t="inlineStr"/>
+      <c r="AU19" s="2" t="inlineStr"/>
+      <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" s="2" t="inlineStr"/>
+      <c r="AX19" s="2" t="inlineStr"/>
+      <c r="AY19" s="2" t="inlineStr"/>
+      <c r="AZ19" s="2" t="inlineStr"/>
+      <c r="BA19" s="2" t="inlineStr"/>
+      <c r="BB19" s="2" t="inlineStr">
+        <is>
+          <t>EL</t>
+        </is>
+      </c>
+      <c r="BC19" s="2" t="inlineStr">
         <is>
           <t>主體證據不足</t>
         </is>
       </c>
-      <c r="BD19" s="5" t="inlineStr">
-        <is>
-          <t>COST</t>
-        </is>
-      </c>
-      <c r="BE19" s="5" t="inlineStr"/>
-      <c r="BF19" s="5" t="inlineStr"/>
-      <c r="BG19" s="5" t="inlineStr"/>
-      <c r="BH19" s="5" t="inlineStr"/>
+      <c r="BD19" s="2" t="inlineStr">
+        <is>
+          <t>EL</t>
+        </is>
+      </c>
+      <c r="BE19" s="2" t="inlineStr"/>
+      <c r="BF19" s="2" t="inlineStr"/>
+      <c r="BG19" s="2" t="inlineStr"/>
+      <c r="BH19" s="2" t="inlineStr"/>
+      <c r="BI19" s="2" t="inlineStr"/>
+      <c r="BJ19" s="2" t="inlineStr"/>
+      <c r="BK19" s="2" t="inlineStr"/>
+      <c r="BL19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -18537,12 +18621,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17T01:44:00+08:00</t>
+          <t>2026-08-17T01:02:00+08:00</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>'Mother Nature always wins' | Flood waters cut through Hazel Dell Parkway bridge, crews asking for space as they work to assess damage</t>
+          <t>WATCH: Drone footage shows Hazel Dell Parkway bridge collapse after flooding</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
@@ -18583,7 +18667,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>'-0.791</t>
+          <t>'-0.647</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr"/>
@@ -18597,7 +18681,7 @@
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAJBVV95cUxOU2dmNWppUU1Sbm1ZM3JSWGNUSy1McFNORVExYWJ5LVFfZ3dlZHZjQ015VHpBWGtoSFQ2RmQyb1VkQ2NMS3lMZEpaUEZ4UDRqLVVOajB5UEM1aVU5cks0Z2s5dk4xWDZmWnhwTDVKN1hQbEZKLWxneDUwVjRPR0w2dXh6RmM3YlphYWhuTlFKcmRBNnF4aHYzS2pHa00xS1QwbVcwaDVyLThGQ3ZnbUlPMFRUS1JLSmloc0U4OFV4SVZfNDZvelJnOXpmTENwWE8xSjc2VUt3NFpjb29aR3VmaG9uT2hzUWRrTTNGeWUxaUYybTA0dzdUcXJ6ZngyQy1SU0Fpb2U5dkVFdHROYWlrRFVvRWpJeTF5d25YUDZNejBZY1lkc2lXdjBrcVF2OUstbUhhTlB6YjdSX05paXdpMmE4Mlk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxPcUJQRDFZcG1KbTJ3ZmwxaExQNTAyZzIyRGpUYkFpd3dvalBWc1NPNHBkZUhwZ0dmLWZIWlZQU0VLcE90Ukp5SGxGSTdCZjB4M0dvQUljdG9NbTZUSjBlRTJyLWJPLVhQM1dZYWEwLU1hYl9zWXhvNy1wX0N3S2lqNFV1d2NsbnV4MWl0Tmp2UGhzcjBJem5nTUNPNUx3TG9wQmdFZ2NMUVA2eFFyRWd4QUJib1E5cFdxN2h5a1ZXX0RrRTNlYjlzSzJsVWt6OU41eXZKR3RNdkM3dnlhdkJueXV6UlMzcGtsd193cE8ycnQ4MUdjYjR1RUNR?oc=5</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
@@ -18607,7 +18691,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>「大自然總是勝利」|洪水沖垮了 Hazel Dell Parkway 大橋，工作人員在評估損失時要求騰出空間</t>
+          <t>觀看：無人機鏡頭顯示 Hazel Dell Parkway 橋樑在洪水後倒塌</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
@@ -18622,19 +18706,19 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>flood</t>
+          <t>flood；flooding</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr"/>
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>ca87d494360b0f73a396d9be</t>
+          <t>b079310396e547e032e1ec1b</t>
         </is>
       </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>de88dbbab1bc44a277cf9d86</t>
+          <t>0b541c2e752404d4465b6fe5</t>
         </is>
       </c>
       <c r="AE20" s="2" t="inlineStr"/>
@@ -18691,349 +18775,13 @@
       </c>
       <c r="BG20" s="2" t="inlineStr"/>
       <c r="BH20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr"/>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Estée Lauder Companies (The)</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-17T01:39:25+08:00</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Montana in Far East El Paso reopened after flooding caused overnight closure</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>天災</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>僅紀錄</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>'-0.699</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr"/>
-      <c r="Q21" s="2" t="inlineStr"/>
-      <c r="R21" s="2" t="inlineStr"/>
-      <c r="S21" s="2" t="inlineStr"/>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxONGVFZEI4OF9jSVdIU0NVU08xRnFuaUtBMXR3NkNBOHlRUEFsc2szb1VfODhDeXB4N2pQTFctUnZzV2xsUHBfc05BenVYYkFhRGI4RGozdjZWbV9VX0prTTJpTEh3RWF4WHBoTnJfb281M0d2V1k4UF9VbERjcnNBNzV0VDVKOWxaQUJFUG5Ock9OVER2cmMzR2tnbFRkQkVkaGdxN0Z2S2JKMzBiOTZR?oc=5</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>KVIA</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
-        <is>
-          <t>蒙大拿州遠東地區埃爾帕索在洪水導致夜間關閉後重新開放</t>
-        </is>
-      </c>
-      <c r="X21" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y21" s="2" t="inlineStr">
-        <is>
-          <t>NATURAL_DISASTER</t>
-        </is>
-      </c>
-      <c r="Z21" s="2" t="inlineStr">
-        <is>
-          <t>flood；flooding</t>
-        </is>
-      </c>
-      <c r="AA21" s="2" t="inlineStr"/>
-      <c r="AB21" s="2" t="inlineStr"/>
-      <c r="AC21" s="2" t="inlineStr">
-        <is>
-          <t>8baabf861da98886f444cefa</t>
-        </is>
-      </c>
-      <c r="AD21" s="2" t="inlineStr">
-        <is>
-          <t>242e7a8d72bcf93bd705396c</t>
-        </is>
-      </c>
-      <c r="AE21" s="2" t="inlineStr"/>
-      <c r="AF21" s="2" t="inlineStr"/>
-      <c r="AG21" s="2" t="inlineStr"/>
-      <c r="AH21" s="2" t="inlineStr"/>
-      <c r="AI21" s="2" t="inlineStr"/>
-      <c r="AJ21" s="2" t="inlineStr"/>
-      <c r="AK21" s="2" t="inlineStr"/>
-      <c r="AL21" s="2" t="inlineStr"/>
-      <c r="AM21" s="2" t="inlineStr"/>
-      <c r="AN21" s="2" t="inlineStr"/>
-      <c r="AO21" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP21" s="2" t="inlineStr"/>
-      <c r="AQ21" s="2" t="inlineStr"/>
-      <c r="AR21" s="2" t="inlineStr"/>
-      <c r="AS21" s="2" t="inlineStr"/>
-      <c r="AT21" s="2" t="inlineStr"/>
-      <c r="AU21" s="2" t="inlineStr"/>
-      <c r="AV21" s="2" t="inlineStr"/>
-      <c r="AW21" s="2" t="inlineStr"/>
-      <c r="AX21" s="2" t="inlineStr"/>
-      <c r="AY21" s="2" t="inlineStr"/>
-      <c r="AZ21" s="2" t="inlineStr"/>
-      <c r="BA21" s="2" t="inlineStr"/>
-      <c r="BB21" s="2" t="inlineStr">
-        <is>
-          <t>EL</t>
-        </is>
-      </c>
-      <c r="BC21" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD21" s="2" t="inlineStr">
-        <is>
-          <t>EL</t>
-        </is>
-      </c>
-      <c r="BE21" s="2" t="inlineStr"/>
-      <c r="BF21" s="2" t="inlineStr"/>
-      <c r="BG21" s="2" t="inlineStr"/>
-      <c r="BH21" s="2" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr"/>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Dell Technologies</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-17T01:02:00+08:00</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>WATCH: Drone footage shows Hazel Dell Parkway bridge collapse after flooding</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>天災</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>僅紀錄</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>'-0.647</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr"/>
-      <c r="Q22" s="2" t="inlineStr"/>
-      <c r="R22" s="2" t="inlineStr"/>
-      <c r="S22" s="2" t="inlineStr"/>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxPcUJQRDFZcG1KbTJ3ZmwxaExQNTAyZzIyRGpUYkFpd3dvalBWc1NPNHBkZUhwZ0dmLWZIWlZQU0VLcE90Ukp5SGxGSTdCZjB4M0dvQUljdG9NbTZUSjBlRTJyLWJPLVhQM1dZYWEwLU1hYl9zWXhvNy1wX0N3S2lqNFV1d2NsbnV4MWl0Tmp2UGhzcjBJem5nTUNPNUx3TG9wQmdFZ2NMUVA2eFFyRWd4QUJib1E5cFdxN2h5a1ZXX0RrRTNlYjlzSzJsVWt6OU41eXZKR3RNdkM3dnlhdkJueXV6UlMzcGtsd193cE8ycnQ4MUdjYjR1RUNR?oc=5</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>WTHR</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>觀看：無人機鏡頭顯示 Hazel Dell Parkway 橋樑在洪水後倒塌</t>
-        </is>
-      </c>
-      <c r="X22" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y22" s="2" t="inlineStr">
-        <is>
-          <t>NATURAL_DISASTER</t>
-        </is>
-      </c>
-      <c r="Z22" s="2" t="inlineStr">
-        <is>
-          <t>flood；flooding</t>
-        </is>
-      </c>
-      <c r="AA22" s="2" t="inlineStr"/>
-      <c r="AB22" s="2" t="inlineStr"/>
-      <c r="AC22" s="2" t="inlineStr">
-        <is>
-          <t>b079310396e547e032e1ec1b</t>
-        </is>
-      </c>
-      <c r="AD22" s="2" t="inlineStr">
-        <is>
-          <t>0b541c2e752404d4465b6fe5</t>
-        </is>
-      </c>
-      <c r="AE22" s="2" t="inlineStr"/>
-      <c r="AF22" s="2" t="inlineStr"/>
-      <c r="AG22" s="2" t="inlineStr"/>
-      <c r="AH22" s="2" t="inlineStr"/>
-      <c r="AI22" s="2" t="inlineStr"/>
-      <c r="AJ22" s="2" t="inlineStr"/>
-      <c r="AK22" s="2" t="inlineStr"/>
-      <c r="AL22" s="2" t="inlineStr"/>
-      <c r="AM22" s="2" t="inlineStr"/>
-      <c r="AN22" s="2" t="inlineStr"/>
-      <c r="AO22" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP22" s="2" t="inlineStr"/>
-      <c r="AQ22" s="2" t="inlineStr"/>
-      <c r="AR22" s="2" t="inlineStr"/>
-      <c r="AS22" s="2" t="inlineStr"/>
-      <c r="AT22" s="2" t="inlineStr"/>
-      <c r="AU22" s="2" t="inlineStr"/>
-      <c r="AV22" s="2" t="inlineStr"/>
-      <c r="AW22" s="2" t="inlineStr"/>
-      <c r="AX22" s="2" t="inlineStr"/>
-      <c r="AY22" s="2" t="inlineStr"/>
-      <c r="AZ22" s="2" t="inlineStr"/>
-      <c r="BA22" s="2" t="inlineStr"/>
-      <c r="BB22" s="2" t="inlineStr">
-        <is>
-          <t>DELL</t>
-        </is>
-      </c>
-      <c r="BC22" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD22" s="2" t="inlineStr">
-        <is>
-          <t>DELL</t>
-        </is>
-      </c>
-      <c r="BE22" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF22" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG22" s="2" t="inlineStr"/>
-      <c r="BH22" s="2" t="inlineStr"/>
+      <c r="BI20" s="2" t="inlineStr"/>
+      <c r="BJ20" s="2" t="inlineStr"/>
+      <c r="BK20" s="2" t="inlineStr"/>
+      <c r="BL20" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH22"/>
+  <autoFilter ref="A1:BL20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19044,7 +18792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH1"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -19107,6 +18855,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19410,9 +19162,29 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH1"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19423,7 +19195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA5"/>
+  <dimension ref="A1:AA8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -19473,134 +19245,134 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>methods</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>started_at</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>finished_at</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>llm_calls</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>cache_reused</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>selected_company_count</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>collected</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>rows</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>errors</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>stages</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>quota_reserved</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>重複合併</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>sources</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>rows</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>changed</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>missing_publication_time</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>ticker_statuses</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>llm_calls</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>start</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>methods</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>ai</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>cache_reused</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>major</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>selected_company_count</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>collected</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>errors</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>stages</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>quota_reserved</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>重複合併</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ticker-audit-20261024-081549</t>
+          <t>daily-2026-10-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>ticker-audit</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -19610,46 +19382,80 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T08:15:49.296780+08:00</t>
+          <t>2026-10-25T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T08:15:49.296790+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>1691</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>257</v>
-      </c>
-      <c r="I2" s="2" t="n">
+          <t>2026-10-26T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:23:38.366332+08:00</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:40:53.776257+08:00</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr"/>
-      <c r="T2" s="2" t="inlineStr"/>
-      <c r="U2" s="2" t="inlineStr"/>
-      <c r="V2" s="2" t="inlineStr"/>
-      <c r="W2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="n">
+        <v>1926</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>503</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>1976</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>1961</v>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 16 筆', '方法二 1958 筆；公司 503 家（非輪替）', '市場事件搜尋 2 筆', 'FinBERT 完成 1976 筆']</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>1961</v>
+      </c>
+      <c r="W2" s="2" t="n">
+        <v>15</v>
+      </c>
       <c r="X2" s="2" t="inlineStr"/>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -19658,12 +19464,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+          <t>daily-2026-10-25</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -19673,90 +19479,94 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:26:34.299718+08:00</t>
+          <t>2026-10-24T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:32:11.776786+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr"/>
+          <t>2026-10-25T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:23:17.137147+08:00</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:40:12.120180+08:00</t>
+        </is>
+      </c>
       <c r="K3" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="b">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>2032</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>503</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>34</v>
+        <v>2089</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="T3" s="2" t="n">
-        <v>17</v>
+        <v>2067</v>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 26 筆', '方法二 2059 筆；公司 503 家（非輪替）', '市場事件搜尋 6 筆', 'FinBERT 完成 2089 筆']</t>
+        </is>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X3" s="2" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
-      </c>
-      <c r="Y3" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="Z3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>2067</v>
+      </c>
+      <c r="W3" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="X3" s="2" t="inlineStr"/>
+      <c r="Y3" s="2" t="inlineStr"/>
+      <c r="Z3" s="2" t="inlineStr"/>
+      <c r="AA3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+          <t>daily-2026-10-24</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -19766,94 +19576,94 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:20:47.845317+08:00</t>
+          <t>2026-10-23T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:21:20.302846+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr"/>
+          <t>2026-10-24T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T12:44:09.884829+08:00</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T13:04:34.984103+08:00</t>
+        </is>
+      </c>
       <c r="K4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="b">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>3760</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>503</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>2</v>
+        <v>3802</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" s="2" t="n">
-        <v>2</v>
+        <v>3825</v>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 158 筆', '方法二 3638 筆；公司 503 家（非輪替）', '市場事件搜尋 8 筆', 'FinBERT 完成 3802 筆']</t>
+        </is>
       </c>
       <c r="U4" s="2" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X4" s="2" t="inlineStr">
-        <is>
-          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
-        </is>
-      </c>
-      <c r="Y4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA4" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>3793</v>
+      </c>
+      <c r="W4" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="X4" s="2" t="inlineStr"/>
+      <c r="Y4" s="2" t="inlineStr"/>
+      <c r="Z4" s="2" t="inlineStr"/>
+      <c r="AA4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>ticker-audit-20261024-081549</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>ticker-audit</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -19861,89 +19671,342 @@
           <t>success</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:19:11.949238+08:00</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:19:18.833437+08:00</t>
-        </is>
-      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="n">
-        <v>33</v>
-      </c>
+      <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296780+08:00</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296790+08:00</t>
+        </is>
+      </c>
       <c r="K5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="2" t="n">
-        <v>33</v>
-      </c>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
       <c r="R5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="T5" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="U5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X5" s="2" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
+        <v>1691</v>
+      </c>
+      <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr"/>
+      <c r="V5" s="2" t="inlineStr"/>
+      <c r="W5" s="2" t="inlineStr"/>
+      <c r="X5" s="2" t="n">
+        <v>19</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>1</v>
+        <v>257</v>
       </c>
       <c r="Z5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA5" s="2" t="n">
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
+          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:34.299718+08:00</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:32:11.776786+08:00</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="M6" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N6" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="V6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="2" t="inlineStr"/>
+      <c r="Y6" s="2" t="inlineStr"/>
+      <c r="Z6" s="2" t="inlineStr"/>
+      <c r="AA6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:20:47.845317+08:00</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:21:20.302846+08:00</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="W7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="2" t="inlineStr"/>
+      <c r="Y7" s="2" t="inlineStr"/>
+      <c r="Z7" s="2" t="inlineStr"/>
+      <c r="AA7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:19:11.949238+08:00</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:19:18.833437+08:00</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="2" t="inlineStr"/>
+      <c r="Y8" s="2" t="inlineStr"/>
+      <c r="Z8" s="2" t="inlineStr"/>
+      <c r="AA8" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA5"/>
+  <autoFilter ref="A1:AA8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/news_daily/2026-08-17.xlsx
+++ b/news_daily/2026-08-17.xlsx
@@ -2246,28 +2246,32 @@
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -2311,7 +2315,7 @@
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
@@ -2320,7 +2324,11 @@
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr"/>
-      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>d4fcb35a882c42c3a4e8aec3c6f44b61</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
           <t>2d8c6769d70e39fd7354b721</t>
@@ -2341,7 +2349,11 @@
       <c r="AL9" s="2" t="inlineStr"/>
       <c r="AM9" s="2" t="inlineStr"/>
       <c r="AN9" s="2" t="inlineStr"/>
-      <c r="AO9" s="2" t="inlineStr"/>
+      <c r="AO9" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP9" s="2" t="inlineStr"/>
       <c r="AQ9" s="2" t="inlineStr"/>
       <c r="AR9" s="2" t="inlineStr"/>
@@ -2377,10 +2389,22 @@
         </is>
       </c>
       <c r="BH9" s="2" t="inlineStr"/>
-      <c r="BI9" s="2" t="inlineStr"/>
+      <c r="BI9" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ9" s="2" t="inlineStr"/>
-      <c r="BK9" s="2" t="inlineStr"/>
-      <c r="BL9" s="2" t="inlineStr"/>
+      <c r="BK9" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2602,28 +2626,32 @@
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -2667,7 +2695,7 @@
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
@@ -2676,7 +2704,11 @@
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr"/>
-      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>71a7c03684154117aba91f7bab42dd66</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
           <t>bbf69bd4e360277b64575fec</t>
@@ -2697,7 +2729,11 @@
       <c r="AL11" s="2" t="inlineStr"/>
       <c r="AM11" s="2" t="inlineStr"/>
       <c r="AN11" s="2" t="inlineStr"/>
-      <c r="AO11" s="2" t="inlineStr"/>
+      <c r="AO11" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP11" s="2" t="inlineStr"/>
       <c r="AQ11" s="2" t="inlineStr"/>
       <c r="AR11" s="2" t="inlineStr"/>
@@ -2741,10 +2777,22 @@
         </is>
       </c>
       <c r="BH11" s="2" t="inlineStr"/>
-      <c r="BI11" s="2" t="inlineStr"/>
+      <c r="BI11" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ11" s="2" t="inlineStr"/>
-      <c r="BK11" s="2" t="inlineStr"/>
-      <c r="BL11" s="2" t="inlineStr"/>
+      <c r="BK11" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2780,28 +2828,32 @@
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -2845,7 +2897,7 @@
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
@@ -2854,7 +2906,11 @@
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr"/>
-      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>acee026b1f7846138753d4f25f956547</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
           <t>1377ef636e8ca997c6ab2bfa</t>
@@ -2875,7 +2931,11 @@
       <c r="AL12" s="2" t="inlineStr"/>
       <c r="AM12" s="2" t="inlineStr"/>
       <c r="AN12" s="2" t="inlineStr"/>
-      <c r="AO12" s="2" t="inlineStr"/>
+      <c r="AO12" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP12" s="2" t="inlineStr"/>
       <c r="AQ12" s="2" t="inlineStr"/>
       <c r="AR12" s="2" t="inlineStr"/>
@@ -2919,10 +2979,22 @@
         </is>
       </c>
       <c r="BH12" s="2" t="inlineStr"/>
-      <c r="BI12" s="2" t="inlineStr"/>
+      <c r="BI12" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ12" s="2" t="inlineStr"/>
-      <c r="BK12" s="2" t="inlineStr"/>
-      <c r="BL12" s="2" t="inlineStr"/>
+      <c r="BK12" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3924,28 +3996,32 @@
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -3989,7 +4065,7 @@
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
@@ -3998,7 +4074,11 @@
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr"/>
-      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>6dd4fa28f3224bf6b6e60d90e3610431</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
           <t>07ef2468e0f84285d533b85c</t>
@@ -4019,7 +4099,11 @@
       <c r="AL18" s="2" t="inlineStr"/>
       <c r="AM18" s="2" t="inlineStr"/>
       <c r="AN18" s="2" t="inlineStr"/>
-      <c r="AO18" s="2" t="inlineStr"/>
+      <c r="AO18" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP18" s="2" t="inlineStr"/>
       <c r="AQ18" s="2" t="inlineStr"/>
       <c r="AR18" s="2" t="inlineStr"/>
@@ -4063,10 +4147,22 @@
         </is>
       </c>
       <c r="BH18" s="2" t="inlineStr"/>
-      <c r="BI18" s="2" t="inlineStr"/>
+      <c r="BI18" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ18" s="2" t="inlineStr"/>
-      <c r="BK18" s="2" t="inlineStr"/>
-      <c r="BL18" s="2" t="inlineStr"/>
+      <c r="BK18" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -5056,28 +5152,32 @@
       <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -5121,7 +5221,7 @@
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
@@ -5130,7 +5230,11 @@
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr"/>
-      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>ac7baf9645cc4f8b9fc54eb37063db2a</t>
+        </is>
+      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
           <t>42b38809a45e5487206ca731</t>
@@ -5151,7 +5255,11 @@
       <c r="AL24" s="2" t="inlineStr"/>
       <c r="AM24" s="2" t="inlineStr"/>
       <c r="AN24" s="2" t="inlineStr"/>
-      <c r="AO24" s="2" t="inlineStr"/>
+      <c r="AO24" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP24" s="2" t="inlineStr"/>
       <c r="AQ24" s="2" t="inlineStr"/>
       <c r="AR24" s="2" t="inlineStr"/>
@@ -5195,10 +5303,22 @@
         </is>
       </c>
       <c r="BH24" s="2" t="inlineStr"/>
-      <c r="BI24" s="2" t="inlineStr"/>
+      <c r="BI24" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ24" s="2" t="inlineStr"/>
-      <c r="BK24" s="2" t="inlineStr"/>
-      <c r="BL24" s="2" t="inlineStr"/>
+      <c r="BK24" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -6422,28 +6542,32 @@
       <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -6487,7 +6611,7 @@
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
@@ -6496,7 +6620,11 @@
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr"/>
-      <c r="AB31" s="2" t="inlineStr"/>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>1952c209b91545a58f5c274083110f00</t>
+        </is>
+      </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
           <t>ea8a77591730a75e337dd6c7</t>
@@ -6517,7 +6645,11 @@
       <c r="AL31" s="2" t="inlineStr"/>
       <c r="AM31" s="2" t="inlineStr"/>
       <c r="AN31" s="2" t="inlineStr"/>
-      <c r="AO31" s="2" t="inlineStr"/>
+      <c r="AO31" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP31" s="2" t="inlineStr"/>
       <c r="AQ31" s="2" t="inlineStr"/>
       <c r="AR31" s="2" t="inlineStr"/>
@@ -6561,10 +6693,22 @@
         </is>
       </c>
       <c r="BH31" s="2" t="inlineStr"/>
-      <c r="BI31" s="2" t="inlineStr"/>
+      <c r="BI31" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ31" s="2" t="inlineStr"/>
-      <c r="BK31" s="2" t="inlineStr"/>
-      <c r="BL31" s="2" t="inlineStr"/>
+      <c r="BK31" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL31" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6996,28 +7140,32 @@
       <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -7061,7 +7209,7 @@
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -7070,7 +7218,11 @@
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr"/>
-      <c r="AB34" s="2" t="inlineStr"/>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>ad09814b9f7c49a8b1d4caff903c328a</t>
+        </is>
+      </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
           <t>c5ffaa47260e1e72b074546d</t>
@@ -7091,7 +7243,11 @@
       <c r="AL34" s="2" t="inlineStr"/>
       <c r="AM34" s="2" t="inlineStr"/>
       <c r="AN34" s="2" t="inlineStr"/>
-      <c r="AO34" s="2" t="inlineStr"/>
+      <c r="AO34" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP34" s="2" t="inlineStr"/>
       <c r="AQ34" s="2" t="inlineStr"/>
       <c r="AR34" s="2" t="inlineStr"/>
@@ -7135,10 +7291,22 @@
         </is>
       </c>
       <c r="BH34" s="2" t="inlineStr"/>
-      <c r="BI34" s="2" t="inlineStr"/>
+      <c r="BI34" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ34" s="2" t="inlineStr"/>
-      <c r="BK34" s="2" t="inlineStr"/>
-      <c r="BL34" s="2" t="inlineStr"/>
+      <c r="BK34" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7174,28 +7342,32 @@
       <c r="G35" s="2" t="inlineStr"/>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -7239,7 +7411,7 @@
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
@@ -7248,7 +7420,11 @@
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr"/>
-      <c r="AB35" s="2" t="inlineStr"/>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>118a661fdcb9448b95a5ce007735066d</t>
+        </is>
+      </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
           <t>17fe9902e4655c85a40a4c4f</t>
@@ -7269,7 +7445,11 @@
       <c r="AL35" s="2" t="inlineStr"/>
       <c r="AM35" s="2" t="inlineStr"/>
       <c r="AN35" s="2" t="inlineStr"/>
-      <c r="AO35" s="2" t="inlineStr"/>
+      <c r="AO35" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP35" s="2" t="inlineStr"/>
       <c r="AQ35" s="2" t="inlineStr"/>
       <c r="AR35" s="2" t="inlineStr"/>
@@ -7313,10 +7493,22 @@
         </is>
       </c>
       <c r="BH35" s="2" t="inlineStr"/>
-      <c r="BI35" s="2" t="inlineStr"/>
+      <c r="BI35" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ35" s="2" t="inlineStr"/>
-      <c r="BK35" s="2" t="inlineStr"/>
-      <c r="BL35" s="2" t="inlineStr"/>
+      <c r="BK35" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL35" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
@@ -8330,28 +8522,32 @@
       <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -8395,7 +8591,7 @@
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
@@ -8404,7 +8600,11 @@
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr"/>
-      <c r="AB41" s="2" t="inlineStr"/>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>69ed44873c13490a94ef1a180e69e3f5</t>
+        </is>
+      </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
           <t>511bfbc9e677d18004bfbefd</t>
@@ -8425,7 +8625,11 @@
       <c r="AL41" s="2" t="inlineStr"/>
       <c r="AM41" s="2" t="inlineStr"/>
       <c r="AN41" s="2" t="inlineStr"/>
-      <c r="AO41" s="2" t="inlineStr"/>
+      <c r="AO41" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP41" s="2" t="inlineStr"/>
       <c r="AQ41" s="2" t="inlineStr"/>
       <c r="AR41" s="2" t="inlineStr"/>
@@ -8469,10 +8673,22 @@
         </is>
       </c>
       <c r="BH41" s="2" t="inlineStr"/>
-      <c r="BI41" s="2" t="inlineStr"/>
+      <c r="BI41" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ41" s="2" t="inlineStr"/>
-      <c r="BK41" s="2" t="inlineStr"/>
-      <c r="BL41" s="2" t="inlineStr"/>
+      <c r="BK41" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL41" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8710,28 +8926,32 @@
       <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -8775,7 +8995,7 @@
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
@@ -8784,7 +9004,11 @@
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr"/>
-      <c r="AB43" s="2" t="inlineStr"/>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>e1e447fee9f44123aa4d1f97fe901bb6</t>
+        </is>
+      </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
           <t>92fda83d1814cb0e78fc89b2</t>
@@ -8805,7 +9029,11 @@
       <c r="AL43" s="2" t="inlineStr"/>
       <c r="AM43" s="2" t="inlineStr"/>
       <c r="AN43" s="2" t="inlineStr"/>
-      <c r="AO43" s="2" t="inlineStr"/>
+      <c r="AO43" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP43" s="2" t="inlineStr"/>
       <c r="AQ43" s="2" t="inlineStr"/>
       <c r="AR43" s="2" t="inlineStr"/>
@@ -8841,10 +9069,22 @@
         </is>
       </c>
       <c r="BH43" s="2" t="inlineStr"/>
-      <c r="BI43" s="2" t="inlineStr"/>
+      <c r="BI43" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ43" s="2" t="inlineStr"/>
-      <c r="BK43" s="2" t="inlineStr"/>
-      <c r="BL43" s="2" t="inlineStr"/>
+      <c r="BK43" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL43" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -9644,28 +9884,32 @@
       <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -9709,7 +9953,7 @@
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
@@ -9718,7 +9962,11 @@
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr"/>
-      <c r="AB48" s="2" t="inlineStr"/>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>1076918af7fc47dea732195d67f5a81e</t>
+        </is>
+      </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
           <t>a3b092e55aac6ffdfead4203</t>
@@ -9739,7 +9987,11 @@
       <c r="AL48" s="2" t="inlineStr"/>
       <c r="AM48" s="2" t="inlineStr"/>
       <c r="AN48" s="2" t="inlineStr"/>
-      <c r="AO48" s="2" t="inlineStr"/>
+      <c r="AO48" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP48" s="2" t="inlineStr"/>
       <c r="AQ48" s="2" t="inlineStr"/>
       <c r="AR48" s="2" t="inlineStr"/>
@@ -9775,10 +10027,22 @@
         </is>
       </c>
       <c r="BH48" s="2" t="inlineStr"/>
-      <c r="BI48" s="2" t="inlineStr"/>
+      <c r="BI48" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ48" s="2" t="inlineStr"/>
-      <c r="BK48" s="2" t="inlineStr"/>
-      <c r="BL48" s="2" t="inlineStr"/>
+      <c r="BK48" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL48" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9814,28 +10078,32 @@
       <c r="G49" s="2" t="inlineStr"/>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -9879,7 +10147,7 @@
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
@@ -9888,7 +10156,11 @@
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr"/>
-      <c r="AB49" s="2" t="inlineStr"/>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>20d343167efb4496b5cfda6ba0ead243</t>
+        </is>
+      </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
           <t>453f9ebf1d60a7feaf5ce2e0</t>
@@ -9909,7 +10181,11 @@
       <c r="AL49" s="2" t="inlineStr"/>
       <c r="AM49" s="2" t="inlineStr"/>
       <c r="AN49" s="2" t="inlineStr"/>
-      <c r="AO49" s="2" t="inlineStr"/>
+      <c r="AO49" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP49" s="2" t="inlineStr"/>
       <c r="AQ49" s="2" t="inlineStr"/>
       <c r="AR49" s="2" t="inlineStr"/>
@@ -9953,10 +10229,22 @@
         </is>
       </c>
       <c r="BH49" s="2" t="inlineStr"/>
-      <c r="BI49" s="2" t="inlineStr"/>
+      <c r="BI49" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ49" s="2" t="inlineStr"/>
-      <c r="BK49" s="2" t="inlineStr"/>
-      <c r="BL49" s="2" t="inlineStr"/>
+      <c r="BK49" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL49" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -10372,28 +10660,32 @@
       <c r="G52" s="2" t="inlineStr"/>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -10437,7 +10729,7 @@
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -10446,7 +10738,11 @@
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr"/>
-      <c r="AB52" s="2" t="inlineStr"/>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>dfe4adde07ea406ab707f196f3dfb92f</t>
+        </is>
+      </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
           <t>772734891c1e571a51ed9d80</t>
@@ -10467,7 +10763,11 @@
       <c r="AL52" s="2" t="inlineStr"/>
       <c r="AM52" s="2" t="inlineStr"/>
       <c r="AN52" s="2" t="inlineStr"/>
-      <c r="AO52" s="2" t="inlineStr"/>
+      <c r="AO52" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP52" s="2" t="inlineStr"/>
       <c r="AQ52" s="2" t="inlineStr"/>
       <c r="AR52" s="2" t="inlineStr"/>
@@ -10511,10 +10811,22 @@
         </is>
       </c>
       <c r="BH52" s="2" t="inlineStr"/>
-      <c r="BI52" s="2" t="inlineStr"/>
+      <c r="BI52" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ52" s="2" t="inlineStr"/>
-      <c r="BK52" s="2" t="inlineStr"/>
-      <c r="BL52" s="2" t="inlineStr"/>
+      <c r="BK52" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL52" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
